--- a/TUCUMAN 1061/Julio/tucuman Julio.xlsx
+++ b/TUCUMAN 1061/Julio/tucuman Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9394C26-3DF8-4CD5-9DB2-D2AD3C1FC468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0403F209-D254-4EAB-ACB2-C41DC91A76D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -527,9 +527,6 @@
     <t>SALDO ANTERIOR</t>
   </si>
   <si>
-    <t>subidos en mar 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Javier </t>
   </si>
   <si>
@@ -548,12 +545,6 @@
     <t>EDESUR:</t>
   </si>
   <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Servicio de trabajo en impermeabilizacion de terraza - Sr. Lenoardo Balcazza</t>
-  </si>
-  <si>
     <t>Perez Sebastian</t>
   </si>
   <si>
@@ -567,6 +558,9 @@
   </si>
   <si>
     <t>Administraciòn JULIO 2025:</t>
+  </si>
+  <si>
+    <t>subidos en juli 2025</t>
   </si>
 </sst>
 </file>
@@ -574,22 +568,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="14">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.000%"/>
-    <numFmt numFmtId="172" formatCode="0.00000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="0.000%"/>
+    <numFmt numFmtId="175" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -836,6 +830,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1370,16 +1372,16 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1395,87 +1397,86 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1484,7 +1485,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1497,22 +1498,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1522,26 +1523,26 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="167" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1553,34 +1554,34 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="37" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="37" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="38" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8" quotePrefix="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="13" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="28" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1"/>
@@ -1610,10 +1611,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1625,11 +1626,11 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1642,7 +1643,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1654,9 +1654,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1668,8 +1668,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="29" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1781,7 +1781,7 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1811,6 +1811,7 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="37" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2209,15 +2210,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2227,7 +2228,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -2237,18 +2238,18 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="194">
+      <c r="E3" s="192">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="194"/>
+      <c r="F3" s="192"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -2258,18 +2259,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="D5" s="42" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -2277,13 +2278,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2293,11 +2294,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -2306,7 +2307,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2316,19 +2317,19 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="204" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="204"/>
-      <c r="C12" s="204"/>
-      <c r="D12" s="204"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="204"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="202"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -2338,7 +2339,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>60</v>
       </c>
@@ -2350,13 +2351,13 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="44">
+      <c r="H14" s="189">
         <v>373590.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>160</v>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="98" t="s">
+        <v>162</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2364,65 +2365,64 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="44">
-        <f>H14/2</f>
-        <v>186795.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="99" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="191">
+      <c r="H15" s="189">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="184">
-        <f>SUM(H13:H16)</f>
-        <v>564416.03</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="43"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="205" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="182">
+        <f>SUM(H13:H15)</f>
+        <v>377620.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="43"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206"/>
-      <c r="H19" s="207"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="204"/>
+      <c r="C18" s="204"/>
+      <c r="D18" s="204"/>
+      <c r="E18" s="204"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="204"/>
+      <c r="H18" s="205"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="188">
+        <v>177932.77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="25"/>
@@ -2430,56 +2430,57 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="190">
-        <v>177932.77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="26">
-        <f>759222.49-400523.88</f>
-        <v>358698.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+      <c r="H20" s="188">
+        <v>358054.16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="27">
-        <f>SUM(H20:H21)</f>
-        <v>536631.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="208" t="s">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="27">
+        <f>SUM(H19:H20)</f>
+        <v>535986.92999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="206" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="208"/>
-      <c r="C23" s="208"/>
-      <c r="D23" s="208"/>
-      <c r="E23" s="208"/>
-      <c r="F23" s="208"/>
-      <c r="G23" s="208"/>
-      <c r="H23" s="208"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="99" t="s">
+      <c r="B22" s="206"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="206"/>
+      <c r="J22" s="26"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="98" t="s">
         <v>142</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="188">
+        <v>42645</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="98" t="s">
+        <v>160</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="25"/>
@@ -2487,278 +2488,271 @@
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="190">
-        <v>42645</v>
+      <c r="H24" s="188">
+        <v>49340</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="99" t="s">
-        <v>163</v>
+    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="98" t="s">
+        <v>144</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="25"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="190">
-        <v>49340</v>
-      </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="99" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="26">
-        <v>550000</v>
-      </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="99" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="190">
+      <c r="H25" s="188">
         <v>65000</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="27">
-        <f>SUM(H24:H27)</f>
-        <v>706985</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="205" t="s">
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="27">
+        <f>SUM(H23:H25)</f>
+        <v>156985</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="203" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="206"/>
-      <c r="C29" s="206"/>
-      <c r="D29" s="206"/>
-      <c r="E29" s="206"/>
-      <c r="F29" s="206"/>
-      <c r="G29" s="206"/>
-      <c r="H29" s="207"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="B27" s="204"/>
+      <c r="C27" s="204"/>
+      <c r="D27" s="204"/>
+      <c r="E27" s="204"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="204"/>
+      <c r="H27" s="205"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
         <v>9</v>
       </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="44"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="237">
+        <v>66600</v>
+      </c>
+      <c r="I29" s="44"/>
+      <c r="N29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
       <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
-        <v>10</v>
-      </c>
+      <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="45"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="176">
-        <v>60592.67</v>
-      </c>
-      <c r="I31" s="45"/>
-      <c r="N31" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="29"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="205" t="s">
+      <c r="H30" s="29"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="203" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="206"/>
-      <c r="D33" s="206"/>
-      <c r="E33" s="206"/>
-      <c r="F33" s="206"/>
-      <c r="G33" s="206"/>
-      <c r="H33" s="207"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="51"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="53"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="B31" s="204"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="204"/>
+      <c r="H31" s="205"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="50"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="52"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="32">
-        <f>H17+H22+H28+H31+H34</f>
-        <v>1868625.08</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A36" s="47" t="s">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="32">
+        <f>H16+H21+H26+H29+H32</f>
+        <v>1137192.71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49"/>
-    </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="195" t="s">
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="48"/>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="193" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="196"/>
-      <c r="C37" s="196"/>
-      <c r="D37" s="196"/>
-      <c r="E37" s="196"/>
-      <c r="F37" s="196"/>
-      <c r="G37" s="196"/>
-      <c r="H37" s="197"/>
-      <c r="I37" s="169"/>
-      <c r="K37" s="169"/>
-    </row>
-    <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="198"/>
-      <c r="B38" s="199"/>
-      <c r="C38" s="199"/>
-      <c r="D38" s="199"/>
-      <c r="E38" s="199"/>
-      <c r="F38" s="199"/>
-      <c r="G38" s="199"/>
-      <c r="H38" s="200"/>
-    </row>
-    <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="209"/>
-      <c r="B39" s="210"/>
-      <c r="C39" s="210"/>
-      <c r="D39" s="210"/>
-      <c r="E39" s="210"/>
-      <c r="F39" s="210"/>
-      <c r="G39" s="211"/>
+      <c r="B35" s="194"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="194"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="194"/>
+      <c r="H35" s="195"/>
+      <c r="I35" s="168"/>
+      <c r="K35" s="168"/>
+    </row>
+    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="196"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="198"/>
+    </row>
+    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="207"/>
+      <c r="B37" s="208"/>
+      <c r="C37" s="208"/>
+      <c r="D37" s="208"/>
+      <c r="E37" s="208"/>
+      <c r="F37" s="208"/>
+      <c r="G37" s="209"/>
+      <c r="H37" s="33"/>
+    </row>
+    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="207"/>
+      <c r="B38" s="208"/>
+      <c r="C38" s="208"/>
+      <c r="D38" s="208"/>
+      <c r="E38" s="208"/>
+      <c r="F38" s="208"/>
+      <c r="G38" s="209"/>
+      <c r="H38" s="33"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="210"/>
+      <c r="B39" s="211"/>
+      <c r="C39" s="211"/>
+      <c r="D39" s="211"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="211"/>
+      <c r="G39" s="212"/>
       <c r="H39" s="33"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="209"/>
-      <c r="B40" s="210"/>
-      <c r="C40" s="210"/>
-      <c r="D40" s="210"/>
-      <c r="E40" s="210"/>
-      <c r="F40" s="210"/>
-      <c r="G40" s="211"/>
-      <c r="H40" s="33"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="212"/>
-      <c r="B41" s="213"/>
-      <c r="C41" s="213"/>
-      <c r="D41" s="213"/>
-      <c r="E41" s="213"/>
-      <c r="F41" s="213"/>
-      <c r="G41" s="214"/>
-      <c r="H41" s="33"/>
-    </row>
-    <row r="42" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="215" t="s">
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="216"/>
-      <c r="C42" s="216"/>
-      <c r="D42" s="216"/>
-      <c r="E42" s="216"/>
-      <c r="F42" s="216"/>
-      <c r="G42" s="217"/>
-      <c r="H42" s="34">
-        <f>SUM(H39:H41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="214"/>
+      <c r="C40" s="214"/>
+      <c r="D40" s="214"/>
+      <c r="E40" s="214"/>
+      <c r="F40" s="214"/>
+      <c r="G40" s="215"/>
+      <c r="H40" s="34">
+        <f>SUM(H37:H39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="19"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="190" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="190"/>
+      <c r="C43" s="190"/>
+      <c r="D43" s="190"/>
+      <c r="E43" s="190"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="190"/>
+      <c r="H43" s="32">
+        <f>+H33+H34</f>
+        <v>1137192.71</v>
+      </c>
+      <c r="J43" s="168"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
       <c r="H44" s="19"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="192" t="s">
-        <v>145</v>
-      </c>
-      <c r="B45" s="192"/>
-      <c r="C45" s="192"/>
-      <c r="D45" s="192"/>
-      <c r="E45" s="192"/>
-      <c r="F45" s="192"/>
-      <c r="G45" s="192"/>
-      <c r="H45" s="32">
-        <f>+H35+H36</f>
-        <v>1868625.08</v>
-      </c>
-      <c r="J45" s="169"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="35">
+        <f>H40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -2768,119 +2762,94 @@
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
     </row>
-    <row r="47" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="35">
-        <f>H42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-    </row>
-    <row r="49" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="201" t="s">
+    <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="202"/>
-      <c r="C49" s="202"/>
-      <c r="D49" s="202"/>
-      <c r="E49" s="202"/>
-      <c r="F49" s="202"/>
-      <c r="G49" s="202"/>
-      <c r="H49" s="203"/>
-    </row>
-    <row r="50" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="193" t="s">
+      <c r="B47" s="200"/>
+      <c r="C47" s="200"/>
+      <c r="D47" s="200"/>
+      <c r="E47" s="200"/>
+      <c r="F47" s="200"/>
+      <c r="G47" s="200"/>
+      <c r="H47" s="201"/>
+    </row>
+    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="191" t="s">
         <v>152</v>
       </c>
-      <c r="B50" s="193"/>
-      <c r="C50" s="193"/>
-      <c r="D50" s="193"/>
-      <c r="E50" s="193"/>
-      <c r="F50" s="193"/>
-      <c r="G50" s="193"/>
-      <c r="H50" s="41">
+      <c r="B48" s="191"/>
+      <c r="C48" s="191"/>
+      <c r="D48" s="191"/>
+      <c r="E48" s="191"/>
+      <c r="F48" s="191"/>
+      <c r="G48" s="191"/>
+      <c r="H48" s="41">
         <v>1108407.9439299698</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="46">
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="45">
         <f>Planilla!I31</f>
         <v>2672781.3927473403</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="38">
-        <f>-(H35+H42)</f>
-        <v>-1868625.08</v>
-      </c>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A53" s="39" t="s">
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="38">
+        <f>-(H33+H40)</f>
+        <v>-1137192.71</v>
+      </c>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A51" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="50">
-        <f>SUM(H50:H52)</f>
-        <v>1912564.25667731</v>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="49">
+        <f>SUM(H48:H50)</f>
+        <v>2643996.6266773101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A37:H38"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2897,173 +2866,173 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="56" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="55" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" style="55" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="55" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" style="55" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="55" customWidth="1"/>
-    <col min="12" max="12" width="0.109375" style="55" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" customWidth="1"/>
-    <col min="16" max="16" width="12.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="53" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="54" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="54" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="54" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="54" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="54" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="54" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="str">
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="219" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: JULIO </v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="223"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="93"/>
-      <c r="C2" s="186">
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="220"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="221"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="92"/>
+      <c r="C2" s="184">
         <v>1822930.46</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="89"/>
-      <c r="D3" s="186">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="88"/>
+      <c r="D3" s="184">
         <v>358698.61</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="L3" s="91"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="L3" s="90"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="88"/>
       <c r="C4" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="219"/>
-      <c r="N4" s="219"/>
-      <c r="O4" s="219"/>
-      <c r="P4" s="219"/>
-      <c r="Q4" s="219"/>
-      <c r="R4" s="220"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="89"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="229">
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="218"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="88"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="227">
         <f>D3</f>
         <v>358698.61</v>
       </c>
-      <c r="D5" s="229"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="13"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="L5" s="91"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="L5" s="90"/>
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="88"/>
       <c r="C6" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="229">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="88"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="227">
         <f>C2-D3</f>
         <v>1464231.85</v>
       </c>
-      <c r="D7" s="229"/>
-      <c r="E7" s="90"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="89"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="88"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="87"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="82"/>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="86"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="81"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3071,1394 +3040,1394 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="81" t="s">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="79" t="s">
+      <c r="F10" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="78" t="s">
+      <c r="J10" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="78" t="s">
+      <c r="K10" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="78" t="s">
+      <c r="L10" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="N10" s="77" t="s">
+      <c r="N10" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="P10" s="77" t="s">
+      <c r="O10" s="76" t="s">
+        <v>156</v>
+      </c>
+      <c r="P10" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="77" t="s">
+      <c r="Q10" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="77" t="s">
+      <c r="R10" s="76" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="177" t="s">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="175" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="178"/>
-      <c r="C11" s="179" t="s">
+      <c r="B11" s="176"/>
+      <c r="C11" s="177" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="180" t="s">
+      <c r="D11" s="178" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="165"/>
-      <c r="F11" s="181">
+      <c r="E11" s="164"/>
+      <c r="F11" s="179">
         <v>7.9</v>
       </c>
-      <c r="G11" s="68">
+      <c r="G11" s="67">
         <v>118500.00000000001</v>
       </c>
-      <c r="H11" s="68">
-        <v>0</v>
-      </c>
-      <c r="I11" s="68">
+      <c r="H11" s="67">
+        <v>0</v>
+      </c>
+      <c r="I11" s="67">
         <f>G11</f>
         <v>118500.00000000001</v>
       </c>
-      <c r="J11" s="68" t="e">
+      <c r="J11" s="67" t="e">
         <f>C8*F11/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="68">
+      <c r="K11" s="67">
         <f t="shared" ref="K11:K18" si="0">G11-H11-I11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="68"/>
-      <c r="M11" s="182">
+      <c r="L11" s="67"/>
+      <c r="M11" s="180">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="182">
+      <c r="N11" s="180">
         <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
         <v>0</v>
       </c>
-      <c r="O11" s="68">
+      <c r="O11" s="67">
         <f>C$7*F11/100</f>
         <v>115674.31615000003</v>
       </c>
-      <c r="P11" s="68">
+      <c r="P11" s="67">
         <f t="shared" ref="P11:P30" si="2">C$9*F11/100</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="68">
+      <c r="Q11" s="67">
         <f>C$5*F11/100</f>
         <v>28337.190189999998</v>
       </c>
-      <c r="R11" s="182">
+      <c r="R11" s="180">
         <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
         <v>144011.50634000002</v>
       </c>
-      <c r="U11" s="94" t="s">
+      <c r="U11" s="93" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="170" t="s">
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="169" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="163"/>
-      <c r="C12" s="171" t="s">
+      <c r="B12" s="162"/>
+      <c r="C12" s="170" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="172" t="s">
+      <c r="D12" s="171" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="173"/>
-      <c r="F12" s="174">
+      <c r="E12" s="172"/>
+      <c r="F12" s="173">
         <v>7.9</v>
       </c>
-      <c r="G12" s="161">
+      <c r="G12" s="160">
         <v>118500.00000000001</v>
       </c>
-      <c r="H12" s="161">
-        <v>0</v>
-      </c>
-      <c r="I12" s="68">
+      <c r="H12" s="160">
+        <v>0</v>
+      </c>
+      <c r="I12" s="67">
         <f>G12</f>
         <v>118500.00000000001</v>
       </c>
-      <c r="J12" s="161" t="e">
+      <c r="J12" s="160" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="161">
+      <c r="K12" s="160">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="161"/>
-      <c r="M12" s="167">
+      <c r="L12" s="160"/>
+      <c r="M12" s="166">
         <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
         <v>0</v>
       </c>
-      <c r="N12" s="167">
+      <c r="N12" s="166">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="161">
+      <c r="O12" s="160">
         <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
         <v>115674.31615000003</v>
       </c>
-      <c r="P12" s="161">
+      <c r="P12" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="68">
+      <c r="Q12" s="67">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
         <v>28337.190189999998</v>
       </c>
-      <c r="R12" s="167">
+      <c r="R12" s="166">
         <f t="shared" si="3"/>
         <v>144011.50634000002</v>
       </c>
-      <c r="U12" s="95" t="s">
+      <c r="U12" s="94" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="162" t="s">
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="161" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="163"/>
-      <c r="C13" s="96" t="s">
+      <c r="B13" s="162"/>
+      <c r="C13" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="164" t="s">
+      <c r="D13" s="163" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="165" t="s">
+      <c r="E13" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="166">
+      <c r="F13" s="165">
         <v>7.9</v>
       </c>
-      <c r="G13" s="68">
+      <c r="G13" s="67">
         <v>646653.19954050251</v>
       </c>
-      <c r="H13" s="161">
-        <v>0</v>
-      </c>
-      <c r="I13" s="68">
+      <c r="H13" s="160">
+        <v>0</v>
+      </c>
+      <c r="I13" s="67">
         <f>300000+133890+212770</f>
         <v>646660</v>
       </c>
-      <c r="J13" s="161" t="e">
+      <c r="J13" s="160" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="161">
+      <c r="K13" s="160">
         <f t="shared" si="0"/>
         <v>-6.8004594974918291</v>
       </c>
-      <c r="L13" s="161"/>
-      <c r="M13" s="167">
+      <c r="L13" s="160"/>
+      <c r="M13" s="166">
         <f t="shared" si="4"/>
         <v>-0.20401378492475486</v>
       </c>
-      <c r="N13" s="167">
+      <c r="N13" s="166">
         <f t="shared" si="1"/>
         <v>-7.0044732824165843</v>
       </c>
-      <c r="O13" s="161">
+      <c r="O13" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P13" s="161">
+      <c r="P13" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="68">
+      <c r="Q13" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R13" s="167">
+      <c r="R13" s="166">
         <f t="shared" si="3"/>
         <v>144004.50186671762</v>
       </c>
-      <c r="U13" s="95" t="s">
+      <c r="U13" s="94" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="112" t="s">
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="95" t="s">
+      <c r="B14" s="75"/>
+      <c r="C14" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="158" t="s">
+      <c r="D14" s="157" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="115"/>
-      <c r="F14" s="97">
+      <c r="E14" s="114"/>
+      <c r="F14" s="96">
         <v>7.9</v>
       </c>
-      <c r="G14" s="160">
+      <c r="G14" s="159">
         <v>118497.94000000002</v>
       </c>
-      <c r="H14" s="75"/>
-      <c r="I14" s="68">
+      <c r="H14" s="74"/>
+      <c r="I14" s="67">
         <f>G14</f>
         <v>118497.94000000002</v>
       </c>
-      <c r="J14" s="66" t="e">
+      <c r="J14" s="65" t="e">
         <f>C8*F14/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="66">
+      <c r="K14" s="65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="67"/>
-      <c r="M14" s="65">
+      <c r="L14" s="66"/>
+      <c r="M14" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N14" s="65">
+      <c r="N14" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O14" s="66">
+      <c r="O14" s="65">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P14" s="66">
+      <c r="P14" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="68">
+      <c r="Q14" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R14" s="65">
+      <c r="R14" s="64">
         <f t="shared" si="3"/>
         <v>144011.50634000002</v>
       </c>
-      <c r="U14" s="95" t="s">
+      <c r="U14" s="94" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="112" t="s">
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="95" t="s">
+      <c r="B15" s="71"/>
+      <c r="C15" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="97">
+      <c r="E15" s="114"/>
+      <c r="F15" s="96">
         <v>7.9</v>
       </c>
-      <c r="G15" s="73">
+      <c r="G15" s="72">
         <v>229710.6036811966</v>
       </c>
-      <c r="H15" s="75">
-        <v>0</v>
-      </c>
-      <c r="I15" s="68">
+      <c r="H15" s="74">
+        <v>0</v>
+      </c>
+      <c r="I15" s="67">
         <f>237847-G27</f>
         <v>229710.876712</v>
       </c>
-      <c r="J15" s="66" t="e">
+      <c r="J15" s="65" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="66">
+      <c r="K15" s="65">
         <f t="shared" si="0"/>
         <v>-0.27303080339333974</v>
       </c>
-      <c r="L15" s="66"/>
-      <c r="M15" s="65">
+      <c r="L15" s="65"/>
+      <c r="M15" s="64">
         <f t="shared" si="4"/>
         <v>-8.190924101800192E-3</v>
       </c>
-      <c r="N15" s="65">
+      <c r="N15" s="64">
         <f t="shared" si="1"/>
         <v>-0.28122172749513991</v>
       </c>
-      <c r="O15" s="66">
+      <c r="O15" s="65">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P15" s="66">
+      <c r="P15" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="68">
+      <c r="Q15" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R15" s="65">
+      <c r="R15" s="64">
         <f t="shared" si="3"/>
         <v>144011.22511827253</v>
       </c>
-      <c r="U15" s="95" t="s">
+      <c r="U15" s="94" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="162" t="s">
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="163"/>
-      <c r="C16" s="96" t="s">
+      <c r="B16" s="162"/>
+      <c r="C16" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="164" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="165"/>
-      <c r="F16" s="166">
+      <c r="D16" s="163" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="164"/>
+      <c r="F16" s="165">
         <v>7.9</v>
       </c>
-      <c r="G16" s="68">
+      <c r="G16" s="67">
         <v>824894.30490492634</v>
       </c>
-      <c r="H16" s="161">
-        <v>0</v>
-      </c>
-      <c r="I16" s="68">
+      <c r="H16" s="160">
+        <v>0</v>
+      </c>
+      <c r="I16" s="67">
         <f>888825-I28</f>
         <v>824894.08915568655</v>
       </c>
-      <c r="J16" s="161" t="e">
+      <c r="J16" s="160" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="161">
+      <c r="K16" s="160">
         <f t="shared" si="0"/>
         <v>0.21574923978187144</v>
       </c>
-      <c r="L16" s="161"/>
-      <c r="M16" s="167">
+      <c r="L16" s="160"/>
+      <c r="M16" s="166">
         <f t="shared" si="4"/>
         <v>6.4724771934561425E-3</v>
       </c>
-      <c r="N16" s="167">
+      <c r="N16" s="166">
         <f t="shared" si="1"/>
         <v>0.22222171697532758</v>
       </c>
-      <c r="O16" s="161">
+      <c r="O16" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P16" s="161">
+      <c r="P16" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="68">
+      <c r="Q16" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R16" s="167">
+      <c r="R16" s="166">
         <f t="shared" si="3"/>
         <v>144011.728561717</v>
       </c>
-      <c r="U16" s="95" t="s">
+      <c r="U16" s="94" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="112" t="s">
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="95" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="113" t="s">
+      <c r="D17" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="115" t="s">
+      <c r="E17" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="97">
+      <c r="F17" s="96">
         <v>7.9</v>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="72">
         <v>145557.97902211564</v>
       </c>
-      <c r="H17" s="66">
-        <v>0</v>
-      </c>
-      <c r="I17" s="68">
+      <c r="H17" s="65">
+        <v>0</v>
+      </c>
+      <c r="I17" s="67">
         <f>145554-I23</f>
         <v>137417.876712</v>
       </c>
-      <c r="J17" s="66" t="e">
+      <c r="J17" s="65" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="66">
+      <c r="K17" s="65">
         <f t="shared" si="0"/>
         <v>8140.1023101156461</v>
       </c>
-      <c r="L17" s="66"/>
-      <c r="M17" s="65">
+      <c r="L17" s="65"/>
+      <c r="M17" s="64">
         <f t="shared" si="4"/>
         <v>244.20306930346936</v>
       </c>
-      <c r="N17" s="65">
+      <c r="N17" s="64">
         <f t="shared" si="1"/>
         <v>8384.3053794191146</v>
       </c>
-      <c r="O17" s="66">
+      <c r="O17" s="65">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P17" s="66">
+      <c r="P17" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="68">
+      <c r="Q17" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R17" s="65">
+      <c r="R17" s="64">
         <f t="shared" si="3"/>
         <v>152395.81171941914</v>
       </c>
-      <c r="U17" s="95" t="s">
+      <c r="U17" s="94" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="162" t="s">
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="161" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="163"/>
-      <c r="C18" s="96" t="s">
+      <c r="B18" s="162"/>
+      <c r="C18" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="164" t="s">
+      <c r="D18" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="165" t="s">
+      <c r="E18" s="164" t="s">
         <v>147</v>
       </c>
-      <c r="F18" s="166">
+      <c r="F18" s="165">
         <v>7.9</v>
       </c>
-      <c r="G18" s="68">
+      <c r="G18" s="67">
         <v>313538.37315287697</v>
       </c>
-      <c r="H18" s="161">
-        <v>0</v>
-      </c>
-      <c r="I18" s="68"/>
-      <c r="J18" s="161" t="e">
+      <c r="H18" s="160">
+        <v>0</v>
+      </c>
+      <c r="I18" s="67"/>
+      <c r="J18" s="160" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="161">
+      <c r="K18" s="160">
         <f t="shared" si="0"/>
         <v>313538.37315287697</v>
       </c>
-      <c r="L18" s="161"/>
-      <c r="M18" s="167">
+      <c r="L18" s="160"/>
+      <c r="M18" s="166">
         <f t="shared" si="4"/>
         <v>9406.1511945863094</v>
       </c>
-      <c r="N18" s="167">
+      <c r="N18" s="166">
         <f t="shared" si="1"/>
         <v>322944.52434746327</v>
       </c>
-      <c r="O18" s="161">
+      <c r="O18" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P18" s="161">
+      <c r="P18" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="68">
+      <c r="Q18" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R18" s="167">
+      <c r="R18" s="166">
         <f t="shared" si="3"/>
         <v>466956.0306874633</v>
       </c>
-      <c r="U18" s="95" t="s">
+      <c r="U18" s="94" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="162" t="s">
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="163"/>
-      <c r="C19" s="96" t="s">
+      <c r="B19" s="162"/>
+      <c r="C19" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="164" t="s">
+      <c r="D19" s="163" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="165"/>
-      <c r="F19" s="166">
+      <c r="E19" s="164"/>
+      <c r="F19" s="165">
         <v>7.9</v>
       </c>
-      <c r="G19" s="68">
+      <c r="G19" s="67">
         <v>117558.69960956796</v>
       </c>
-      <c r="H19" s="161">
-        <v>0</v>
-      </c>
-      <c r="I19" s="68">
+      <c r="H19" s="160">
+        <v>0</v>
+      </c>
+      <c r="I19" s="67">
         <f>116620</f>
         <v>116620</v>
       </c>
-      <c r="J19" s="161" t="e">
+      <c r="J19" s="160" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="161">
+      <c r="K19" s="160">
         <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
         <v>938.69960956796422</v>
       </c>
-      <c r="L19" s="161">
+      <c r="L19" s="160">
         <f>G19-I19</f>
         <v>938.69960956796422</v>
       </c>
-      <c r="M19" s="167">
+      <c r="M19" s="166">
         <f t="shared" si="4"/>
         <v>56.321976574077851</v>
       </c>
-      <c r="N19" s="167">
+      <c r="N19" s="166">
         <f t="shared" si="1"/>
         <v>1933.7211957100062</v>
       </c>
-      <c r="O19" s="161">
+      <c r="O19" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P19" s="161">
+      <c r="P19" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="68">
+      <c r="Q19" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R19" s="167">
+      <c r="R19" s="166">
         <f t="shared" si="3"/>
         <v>145945.22753571003</v>
       </c>
-      <c r="U19" s="95" t="s">
+      <c r="U19" s="94" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="112" t="s">
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="95" t="s">
+      <c r="B20" s="71"/>
+      <c r="C20" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="112" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="97">
+      <c r="E20" s="114"/>
+      <c r="F20" s="96">
         <v>7.9</v>
       </c>
-      <c r="G20" s="73">
+      <c r="G20" s="72">
         <v>147005.20617134054</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="68">
+      <c r="H20" s="65"/>
+      <c r="I20" s="67">
         <f>G20</f>
         <v>147005.20617134054</v>
       </c>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66">
+      <c r="J20" s="65"/>
+      <c r="K20" s="65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L20" s="66"/>
-      <c r="M20" s="65">
+      <c r="L20" s="65"/>
+      <c r="M20" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N20" s="65">
+      <c r="N20" s="64">
         <f t="shared" ref="N20:N29" si="8">K20+M20+L20</f>
         <v>0</v>
       </c>
-      <c r="O20" s="66">
+      <c r="O20" s="65">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P20" s="66">
+      <c r="P20" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="68">
+      <c r="Q20" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R20" s="65">
+      <c r="R20" s="64">
         <f t="shared" si="3"/>
         <v>144011.50634000002</v>
       </c>
-      <c r="U20" s="95" t="s">
+      <c r="U20" s="94" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="162" t="s">
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="163"/>
-      <c r="C21" s="96" t="s">
+      <c r="B21" s="162"/>
+      <c r="C21" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="164" t="s">
+      <c r="D21" s="163" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="165" t="s">
+      <c r="E21" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="166">
+      <c r="F21" s="165">
         <v>7.9</v>
       </c>
-      <c r="G21" s="68">
+      <c r="G21" s="67">
         <v>118500.17984677525</v>
       </c>
-      <c r="H21" s="161"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="161"/>
-      <c r="K21" s="161">
+      <c r="H21" s="160"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160">
         <f t="shared" si="7"/>
         <v>118500.17984677525</v>
       </c>
-      <c r="L21" s="161"/>
-      <c r="M21" s="167">
+      <c r="L21" s="160"/>
+      <c r="M21" s="166">
         <f t="shared" si="4"/>
         <v>3555.0053954032574</v>
       </c>
-      <c r="N21" s="167">
+      <c r="N21" s="166">
         <f t="shared" si="8"/>
         <v>122055.18524217852</v>
       </c>
-      <c r="O21" s="161">
+      <c r="O21" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P21" s="161">
+      <c r="P21" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="68">
+      <c r="Q21" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R21" s="167">
+      <c r="R21" s="166">
         <f t="shared" si="3"/>
         <v>266066.69158217852</v>
       </c>
-      <c r="U21" s="95" t="s">
+      <c r="U21" s="94" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="162" t="s">
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="163"/>
-      <c r="C22" s="96" t="s">
+      <c r="B22" s="162"/>
+      <c r="C22" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="164" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="165" t="s">
+      <c r="D22" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F22" s="166">
+      <c r="E22" s="164" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="165">
         <v>7.9</v>
       </c>
-      <c r="G22" s="68">
+      <c r="G22" s="67">
         <v>118500.00000000001</v>
       </c>
-      <c r="H22" s="161"/>
-      <c r="I22" s="68">
+      <c r="H22" s="160"/>
+      <c r="I22" s="67">
         <f>G22</f>
         <v>118500.00000000001</v>
       </c>
-      <c r="J22" s="161"/>
-      <c r="K22" s="161">
+      <c r="J22" s="160"/>
+      <c r="K22" s="160">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L22" s="161"/>
-      <c r="M22" s="167">
+      <c r="L22" s="160"/>
+      <c r="M22" s="166">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N22" s="167">
+      <c r="N22" s="166">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O22" s="161">
+      <c r="O22" s="160">
         <f t="shared" si="5"/>
         <v>115674.31615000003</v>
       </c>
-      <c r="P22" s="161">
+      <c r="P22" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="68">
+      <c r="Q22" s="67">
         <f t="shared" si="6"/>
         <v>28337.190189999998</v>
       </c>
-      <c r="R22" s="167">
+      <c r="R22" s="166">
         <f t="shared" si="3"/>
         <v>144011.50634000002</v>
       </c>
-      <c r="S22" s="183"/>
-      <c r="U22" s="95" t="s">
+      <c r="S22" s="181"/>
+      <c r="U22" s="94" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="112"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="95" t="s">
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="111"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="114" t="str">
+      <c r="D23" s="113" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="115" t="s">
+      <c r="E23" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="97">
+      <c r="F23" s="96">
         <v>0.74</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="72">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H23" s="66"/>
-      <c r="I23" s="68">
+      <c r="H23" s="65"/>
+      <c r="I23" s="67">
         <f>G23</f>
         <v>8136.1232879999998</v>
       </c>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66">
+      <c r="J23" s="65"/>
+      <c r="K23" s="65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L23" s="66"/>
-      <c r="M23" s="65">
+      <c r="L23" s="65"/>
+      <c r="M23" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N23" s="65">
+      <c r="N23" s="64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O23" s="66">
+      <c r="O23" s="65">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P23" s="66">
+      <c r="P23" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="65">
+      <c r="Q23" s="65"/>
+      <c r="R23" s="64">
         <f t="shared" si="3"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="U23" s="95" t="s">
+      <c r="U23" s="94" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="162"/>
-      <c r="B24" s="163"/>
-      <c r="C24" s="96" t="s">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="161"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="168" t="str">
+      <c r="D24" s="167" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="165" t="s">
+      <c r="E24" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="166">
+      <c r="F24" s="165">
         <v>0.74</v>
       </c>
-      <c r="G24" s="68">
+      <c r="G24" s="67">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H24" s="161"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="161"/>
-      <c r="K24" s="161">
+      <c r="H24" s="160"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="160"/>
+      <c r="K24" s="160">
         <f t="shared" si="7"/>
         <v>8136.1232879999998</v>
       </c>
-      <c r="L24" s="161"/>
-      <c r="M24" s="167">
+      <c r="L24" s="160"/>
+      <c r="M24" s="166">
         <f t="shared" si="4"/>
         <v>244.08369863999999</v>
       </c>
-      <c r="N24" s="167">
+      <c r="N24" s="166">
         <f t="shared" si="8"/>
         <v>8380.2069866399997</v>
       </c>
-      <c r="O24" s="161">
+      <c r="O24" s="160">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P24" s="161">
+      <c r="P24" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="161">
+      <c r="Q24" s="160">
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="167">
+      <c r="R24" s="166">
         <f t="shared" si="3"/>
         <v>19215.522676640001</v>
       </c>
-      <c r="U24" s="95" t="s">
+      <c r="U24" s="94" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="112"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="95" t="s">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="111"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="114" t="str">
+      <c r="D25" s="113" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="114"/>
-      <c r="F25" s="97">
+      <c r="E25" s="113"/>
+      <c r="F25" s="96">
         <v>0.74</v>
       </c>
-      <c r="G25" s="73">
+      <c r="G25" s="72">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H25" s="66"/>
-      <c r="I25" s="68">
+      <c r="H25" s="65"/>
+      <c r="I25" s="67">
         <f t="shared" ref="I25" si="9">G25</f>
         <v>8136.1232879999998</v>
       </c>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66">
+      <c r="J25" s="65"/>
+      <c r="K25" s="65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L25" s="66"/>
-      <c r="M25" s="65">
+      <c r="L25" s="65"/>
+      <c r="M25" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N25" s="65">
+      <c r="N25" s="64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O25" s="66">
+      <c r="O25" s="65">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P25" s="66">
+      <c r="P25" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="66">
+      <c r="Q25" s="65">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="65">
+      <c r="R25" s="64">
         <f t="shared" si="3"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="U25" s="95" t="s">
+      <c r="U25" s="94" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="162"/>
-      <c r="B26" s="159"/>
-      <c r="C26" s="96" t="s">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="161"/>
+      <c r="B26" s="158"/>
+      <c r="C26" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="168" t="str">
+      <c r="D26" s="167" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="165" t="s">
+      <c r="E26" s="164" t="s">
         <v>147</v>
       </c>
-      <c r="F26" s="166">
+      <c r="F26" s="165">
         <v>0.74</v>
       </c>
-      <c r="G26" s="68">
+      <c r="G26" s="67">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H26" s="161">
-        <v>0</v>
-      </c>
-      <c r="I26" s="68"/>
-      <c r="J26" s="161" t="e">
+      <c r="H26" s="160">
+        <v>0</v>
+      </c>
+      <c r="I26" s="67"/>
+      <c r="J26" s="160" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="161">
+      <c r="K26" s="160">
         <f t="shared" si="7"/>
         <v>8136.1232879999998</v>
       </c>
-      <c r="L26" s="161"/>
-      <c r="M26" s="167">
+      <c r="L26" s="160"/>
+      <c r="M26" s="166">
         <f t="shared" si="4"/>
         <v>244.08369863999999</v>
       </c>
-      <c r="N26" s="167">
+      <c r="N26" s="166">
         <f t="shared" si="8"/>
         <v>8380.2069866399997</v>
       </c>
-      <c r="O26" s="161">
+      <c r="O26" s="160">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P26" s="161">
+      <c r="P26" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="161">
+      <c r="Q26" s="160">
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="167">
+      <c r="R26" s="166">
         <f t="shared" si="3"/>
         <v>19215.522676640001</v>
       </c>
-      <c r="U26" s="95" t="s">
+      <c r="U26" s="94" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="112"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="95" t="s">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="111"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="114" t="str">
+      <c r="D27" s="113" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="114"/>
-      <c r="F27" s="97">
+      <c r="E27" s="113"/>
+      <c r="F27" s="96">
         <v>0.74</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="72">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H27" s="66">
-        <v>0</v>
-      </c>
-      <c r="I27" s="68">
+      <c r="H27" s="65">
+        <v>0</v>
+      </c>
+      <c r="I27" s="67">
         <f>G27</f>
         <v>8136.1232879999998</v>
       </c>
-      <c r="J27" s="66" t="e">
+      <c r="J27" s="65" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="66">
+      <c r="K27" s="65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L27" s="66"/>
-      <c r="M27" s="65">
+      <c r="L27" s="65"/>
+      <c r="M27" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N27" s="65">
+      <c r="N27" s="64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O27" s="66">
+      <c r="O27" s="65">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P27" s="66">
+      <c r="P27" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="66">
+      <c r="Q27" s="65">
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="65">
+      <c r="R27" s="64">
         <f t="shared" si="3"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="U27" s="95" t="s">
+      <c r="U27" s="94" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="187"/>
-      <c r="B28" s="188"/>
-      <c r="C28" s="96" t="s">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="185"/>
+      <c r="B28" s="186"/>
+      <c r="C28" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="168" t="str">
+      <c r="D28" s="167" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="165"/>
-      <c r="F28" s="189">
+      <c r="E28" s="164"/>
+      <c r="F28" s="187">
         <v>0.74</v>
       </c>
-      <c r="G28" s="68">
+      <c r="G28" s="67">
         <v>63930.91084431341</v>
       </c>
-      <c r="H28" s="68">
-        <v>0</v>
-      </c>
-      <c r="I28" s="68">
+      <c r="H28" s="67">
+        <v>0</v>
+      </c>
+      <c r="I28" s="67">
         <f>G28</f>
         <v>63930.91084431341</v>
       </c>
-      <c r="J28" s="68">
-        <v>0</v>
-      </c>
-      <c r="K28" s="68">
+      <c r="J28" s="67">
+        <v>0</v>
+      </c>
+      <c r="K28" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L28" s="68"/>
-      <c r="M28" s="182">
+      <c r="L28" s="67"/>
+      <c r="M28" s="180">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N28" s="182">
+      <c r="N28" s="180">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O28" s="68">
+      <c r="O28" s="67">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P28" s="68">
+      <c r="P28" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="68">
+      <c r="Q28" s="67">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="182">
+      <c r="R28" s="180">
         <f t="shared" si="3"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="U28" s="95" t="s">
+      <c r="U28" s="94" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="162"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="96" t="s">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="161"/>
+      <c r="B29" s="174"/>
+      <c r="C29" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="168" t="str">
+      <c r="D29" s="167" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="165" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="185">
+      <c r="E29" s="164" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="183">
         <v>0.74</v>
       </c>
-      <c r="G29" s="68">
+      <c r="G29" s="67">
         <v>8136.1232879999998</v>
       </c>
-      <c r="H29" s="161">
-        <v>0</v>
-      </c>
-      <c r="I29" s="68">
+      <c r="H29" s="160">
+        <v>0</v>
+      </c>
+      <c r="I29" s="67">
         <f>G29</f>
         <v>8136.1232879999998</v>
       </c>
-      <c r="J29" s="161" t="e">
+      <c r="J29" s="160" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="161">
+      <c r="K29" s="160">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L29" s="161"/>
-      <c r="M29" s="167">
+      <c r="L29" s="160"/>
+      <c r="M29" s="166">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N29" s="167">
+      <c r="N29" s="166">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O29" s="161">
+      <c r="O29" s="160">
         <f t="shared" si="5"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="P29" s="161">
+      <c r="P29" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="161">
+      <c r="Q29" s="160">
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="167">
+      <c r="R29" s="166">
         <f t="shared" si="3"/>
         <v>10835.315690000001</v>
       </c>
-      <c r="U29" s="96" t="s">
+      <c r="U29" s="95" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="74"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="66">
-        <v>0</v>
-      </c>
-      <c r="I30" s="68"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="73"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="65">
+        <v>0</v>
+      </c>
+      <c r="I30" s="67"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="110"/>
-      <c r="U30" s="95" t="s">
+      <c r="Q30" s="65"/>
+      <c r="R30" s="109"/>
+      <c r="U30" s="94" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="59" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="227"/>
-      <c r="B31" s="228"/>
-      <c r="C31" s="228"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="62">
+    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="225"/>
+      <c r="B31" s="226"/>
+      <c r="C31" s="226"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="61">
         <f>SUM(G11:G30)</f>
         <v>3130164.1365016159</v>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="61">
         <f>SUM(H11:H30)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="63">
+      <c r="I31" s="62">
         <f>SUM(I11:I30)</f>
         <v>2672781.3927473403</v>
       </c>
-      <c r="J31" s="62"/>
-      <c r="K31" s="63">
+      <c r="J31" s="61"/>
+      <c r="K31" s="62">
         <f>SUM(K11:K30)</f>
         <v>457382.74375427479</v>
       </c>
-      <c r="L31" s="62"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="63">
+      <c r="L31" s="61"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="62">
         <f>SUM(O11:O30)</f>
         <v>1463939.0036300013</v>
       </c>
-      <c r="P31" s="63">
+      <c r="P31" s="62">
         <f t="shared" ref="P31" si="10">SUM(P11:P30)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="63">
+      <c r="Q31" s="62">
         <f>SUM(Q11:Q30)</f>
         <v>340046.28227999998</v>
       </c>
-      <c r="R31" s="111">
+      <c r="R31" s="110">
         <f>O31+N31+P31+Q31</f>
         <v>1803985.2859100013</v>
       </c>
-      <c r="U31" s="95" t="s">
+      <c r="U31" s="94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="224" t="s">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="222" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="225"/>
-      <c r="R32" s="226"/>
-      <c r="U32" s="95" t="s">
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="223"/>
+      <c r="I32" s="223"/>
+      <c r="J32" s="223"/>
+      <c r="K32" s="223"/>
+      <c r="L32" s="223"/>
+      <c r="M32" s="223"/>
+      <c r="N32" s="223"/>
+      <c r="O32" s="223"/>
+      <c r="P32" s="223"/>
+      <c r="Q32" s="223"/>
+      <c r="R32" s="224"/>
+      <c r="U32" s="94" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="F33" s="58"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57" t="s">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="F33" s="57"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="57"/>
-      <c r="U33" s="95" t="s">
+      <c r="L33" s="56"/>
+      <c r="U33" s="94" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
-      <c r="M34" s="218"/>
-      <c r="N34" s="218"/>
-      <c r="O34" s="218"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C35" s="218"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="218"/>
-      <c r="I35" s="218"/>
-      <c r="J35" s="218"/>
-      <c r="K35" s="218"/>
-      <c r="L35" s="218"/>
-      <c r="M35" s="218"/>
-      <c r="N35" s="218"/>
-      <c r="O35" s="218"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="218"/>
-      <c r="K36" s="218"/>
-      <c r="L36" s="218"/>
-      <c r="M36" s="218"/>
-      <c r="N36" s="218"/>
-      <c r="O36" s="218"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="218"/>
-      <c r="D37" s="218"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="218"/>
-      <c r="K37" s="218"/>
-      <c r="L37" s="218"/>
-      <c r="M37" s="218"/>
-      <c r="N37" s="218"/>
-      <c r="O37" s="218"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="218"/>
-      <c r="K38" s="218"/>
-      <c r="L38" s="218"/>
-      <c r="M38" s="218"/>
-      <c r="N38" s="218"/>
-      <c r="O38" s="218"/>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="216"/>
+      <c r="M34" s="216"/>
+      <c r="N34" s="216"/>
+      <c r="O34" s="216"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C35" s="216"/>
+      <c r="D35" s="216"/>
+      <c r="E35" s="216"/>
+      <c r="F35" s="216"/>
+      <c r="G35" s="216"/>
+      <c r="H35" s="216"/>
+      <c r="I35" s="216"/>
+      <c r="J35" s="216"/>
+      <c r="K35" s="216"/>
+      <c r="L35" s="216"/>
+      <c r="M35" s="216"/>
+      <c r="N35" s="216"/>
+      <c r="O35" s="216"/>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C36" s="216"/>
+      <c r="D36" s="216"/>
+      <c r="E36" s="216"/>
+      <c r="F36" s="216"/>
+      <c r="G36" s="216"/>
+      <c r="H36" s="216"/>
+      <c r="I36" s="216"/>
+      <c r="J36" s="216"/>
+      <c r="K36" s="216"/>
+      <c r="L36" s="216"/>
+      <c r="M36" s="216"/>
+      <c r="N36" s="216"/>
+      <c r="O36" s="216"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C37" s="216"/>
+      <c r="D37" s="216"/>
+      <c r="E37" s="216"/>
+      <c r="F37" s="216"/>
+      <c r="G37" s="216"/>
+      <c r="H37" s="216"/>
+      <c r="I37" s="216"/>
+      <c r="J37" s="216"/>
+      <c r="K37" s="216"/>
+      <c r="L37" s="216"/>
+      <c r="M37" s="216"/>
+      <c r="N37" s="216"/>
+      <c r="O37" s="216"/>
+    </row>
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="216"/>
+      <c r="D38" s="216"/>
+      <c r="E38" s="216"/>
+      <c r="F38" s="216"/>
+      <c r="G38" s="216"/>
+      <c r="H38" s="216"/>
+      <c r="I38" s="216"/>
+      <c r="J38" s="216"/>
+      <c r="K38" s="216"/>
+      <c r="L38" s="216"/>
+      <c r="M38" s="216"/>
+      <c r="N38" s="216"/>
+      <c r="O38" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4479,1009 +4448,1009 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="116" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="116" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="116" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="116" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="116" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="116" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="116" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="116"/>
-    <col min="13" max="13" width="14.6640625" style="116" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="116" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="116"/>
+    <col min="1" max="1" width="12.140625" style="115" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="115" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="115" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="115" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="115" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="115" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="115" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="115"/>
+    <col min="13" max="13" width="14.7109375" style="115" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="115" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="230" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="228" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="232"/>
-    </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="157"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="156" t="s">
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="230"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="156"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="155" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="153"/>
-    </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="155">
+      <c r="E2" s="152"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="154">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="109">
+      <c r="B3" s="108">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="154">
+      <c r="C3" s="153">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="154">
+      <c r="D3" s="153">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="153" t="s">
+      <c r="E3" s="152" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="116" t="s">
+      <c r="I3" s="115" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="152"/>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="150"/>
-    </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="149"/>
-      <c r="B5" s="149"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-    </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="149"/>
-      <c r="B6" s="149"/>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="233" t="s">
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="151"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="149"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+    </row>
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="148"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="231" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-      <c r="H7" s="235"/>
-      <c r="L7" s="116" t="s">
+      <c r="B7" s="232"/>
+      <c r="C7" s="232"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="233"/>
+      <c r="L7" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="116" t="s">
+      <c r="M7" s="115" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="108">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="107">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="147" t="s">
+      <c r="B8" s="146" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="147" t="s">
+      <c r="C8" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="147" t="s">
+      <c r="D8" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="148">
+      <c r="E8" s="147">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="147" t="s">
+      <c r="F8" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="147" t="s">
+      <c r="G8" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="146" t="s">
+      <c r="H8" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="142">
+      <c r="K8" s="141">
         <v>19</v>
       </c>
-      <c r="L8" s="128">
+      <c r="L8" s="127">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="128">
+      <c r="M8" s="127">
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="145" t="s">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="142">
+      <c r="B9" s="141">
         <v>1617</v>
       </c>
-      <c r="C9" s="142">
+      <c r="C9" s="141">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="142">
+      <c r="D9" s="141">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="105">
+      <c r="E9" s="104">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="104">
+      <c r="F9" s="103">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="104">
+      <c r="G9" s="103">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="103">
+      <c r="H9" s="102">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="116">
+      <c r="K9" s="115">
         <v>106</v>
       </c>
-      <c r="L9" s="128">
+      <c r="L9" s="127">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="116">
+      <c r="M9" s="115">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="116" t="s">
+      <c r="N9" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="O9" s="107">
+      <c r="O9" s="106">
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="143" t="s">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="142">
+      <c r="B10" s="141">
         <v>4104</v>
       </c>
-      <c r="C10" s="142">
+      <c r="C10" s="141">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="142">
+      <c r="D10" s="141">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="105">
+      <c r="E10" s="104">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="104">
+      <c r="F10" s="103">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="104">
+      <c r="G10" s="103">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="103">
+      <c r="H10" s="102">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="115">
         <v>60</v>
       </c>
-      <c r="L10" s="128">
+      <c r="L10" s="127">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="115">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="116" t="s">
+      <c r="N10" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="105">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="143" t="s">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="142">
+      <c r="B11" s="141">
         <v>7644</v>
       </c>
-      <c r="C11" s="142">
+      <c r="C11" s="141">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="142">
+      <c r="D11" s="141">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="105">
+      <c r="E11" s="104">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="104">
+      <c r="F11" s="103">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="104">
+      <c r="G11" s="103">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="103">
+      <c r="H11" s="102">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="116">
+      <c r="K11" s="115">
         <v>79</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="127">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="116">
+      <c r="M11" s="115">
         <v>0.03</v>
       </c>
-      <c r="N11" s="116" t="s">
+      <c r="N11" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="127">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="143" t="s">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="142">
+      <c r="B12" s="141">
         <v>6554</v>
       </c>
-      <c r="C12" s="142">
+      <c r="C12" s="141">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="142">
+      <c r="D12" s="141">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="105">
+      <c r="E12" s="104">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="104">
+      <c r="F12" s="103">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="104">
+      <c r="G12" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="103">
+      <c r="H12" s="102">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="116">
+      <c r="K12" s="115">
         <v>89</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="127">
         <v>400</v>
       </c>
-      <c r="M12" s="116">
+      <c r="M12" s="115">
         <v>253</v>
       </c>
-      <c r="N12" s="116" t="s">
+      <c r="N12" s="115" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="116">
+      <c r="O12" s="115">
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="143" t="s">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="142">
+      <c r="B13" s="141">
         <v>7564</v>
       </c>
-      <c r="C13" s="142">
+      <c r="C13" s="141">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="142">
+      <c r="D13" s="141">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="105">
+      <c r="E13" s="104">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="104">
+      <c r="F13" s="103">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="104">
+      <c r="G13" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="103">
+      <c r="H13" s="102">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="116">
+      <c r="K13" s="115">
         <v>140</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="143">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="116">
+      <c r="M13" s="115">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="143" t="s">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="142">
+      <c r="B14" s="141">
         <v>10119</v>
       </c>
-      <c r="C14" s="142">
+      <c r="C14" s="141">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="142">
+      <c r="D14" s="141">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="105">
+      <c r="E14" s="104">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="104">
+      <c r="F14" s="103">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="104">
+      <c r="G14" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="103">
+      <c r="H14" s="102">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="116">
+      <c r="K14" s="115">
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="143" t="s">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="142">
+      <c r="B15" s="141">
         <v>8986</v>
       </c>
-      <c r="C15" s="142">
+      <c r="C15" s="141">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="142">
+      <c r="D15" s="141">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="105">
+      <c r="E15" s="104">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="104">
+      <c r="F15" s="103">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="104">
+      <c r="G15" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="103">
+      <c r="H15" s="102">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="116">
+      <c r="K15" s="115">
         <v>221</v>
       </c>
-      <c r="L15" s="116">
+      <c r="L15" s="115">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="143" t="s">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="142">
+      <c r="B16" s="141">
         <v>7032</v>
       </c>
-      <c r="C16" s="142">
+      <c r="C16" s="141">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="142">
+      <c r="D16" s="141">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="105">
+      <c r="E16" s="104">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="104">
+      <c r="F16" s="103">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="104">
+      <c r="G16" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="103">
+      <c r="H16" s="102">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="116">
+      <c r="K16" s="115">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="143" t="s">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="142">
+      <c r="B17" s="141">
         <v>1623</v>
       </c>
-      <c r="C17" s="142">
+      <c r="C17" s="141">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="142">
+      <c r="D17" s="141">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="105">
+      <c r="E17" s="104">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="104">
+      <c r="F17" s="103">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="104">
+      <c r="G17" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="103">
+      <c r="H17" s="102">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="116">
+      <c r="K17" s="115">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="143" t="s">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="142">
+      <c r="B18" s="141">
         <v>3932</v>
       </c>
-      <c r="C18" s="142">
+      <c r="C18" s="141">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="142">
+      <c r="D18" s="141">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="105">
+      <c r="E18" s="104">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="104">
+      <c r="F18" s="103">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="104">
+      <c r="G18" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="103">
+      <c r="H18" s="102">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="116">
+      <c r="K18" s="115">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="143" t="s">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="142">
+      <c r="B19" s="141">
         <v>6887</v>
       </c>
-      <c r="C19" s="142">
+      <c r="C19" s="141">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="142">
+      <c r="D19" s="141">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="105">
+      <c r="E19" s="104">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="104">
+      <c r="F19" s="103">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="104">
+      <c r="G19" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="103">
+      <c r="H19" s="102">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="116">
+      <c r="K19" s="115">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="143" t="s">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="142">
+      <c r="B20" s="141">
         <v>1884</v>
       </c>
-      <c r="C20" s="142">
+      <c r="C20" s="141">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="142">
+      <c r="D20" s="141">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="105">
+      <c r="E20" s="104">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="104">
+      <c r="F20" s="103">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="104">
+      <c r="G20" s="103">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="103">
+      <c r="H20" s="102">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="141" t="s">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="140" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="140"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="139">
+      <c r="B21" s="139"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="138">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="138"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="102">
+      <c r="E21" s="137"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="101">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="128">
+      <c r="J21" s="127">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="101">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="100">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="136" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="136"/>
-    </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="100">
+      <c r="L22" s="135"/>
+    </row>
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="99">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="135" t="s">
+      <c r="B23" s="134" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="134"/>
-      <c r="J25" s="116">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="133"/>
+      <c r="J25" s="115">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J26" s="116">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J26" s="115">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J27" s="116">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="115">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="236" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="234" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="237"/>
-      <c r="D28" s="237"/>
-      <c r="E28" s="237"/>
-      <c r="F28" s="238"/>
-      <c r="J28" s="116">
+      <c r="C28" s="235"/>
+      <c r="D28" s="235"/>
+      <c r="E28" s="235"/>
+      <c r="F28" s="236"/>
+      <c r="J28" s="115">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="133" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B29" s="132" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="132" t="s">
+      <c r="C29" s="131" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="132" t="s">
+      <c r="D29" s="131" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="132" t="s">
+      <c r="E29" s="131" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="131" t="s">
+      <c r="F29" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="J29" s="116">
+      <c r="J29" s="115">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B30" s="127" t="s">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B30" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="104">
+      <c r="C30" s="103">
         <v>4000</v>
       </c>
-      <c r="D30" s="104">
-        <v>0</v>
-      </c>
-      <c r="E30" s="125"/>
-      <c r="F30" s="103">
+      <c r="D30" s="103">
+        <v>0</v>
+      </c>
+      <c r="E30" s="124"/>
+      <c r="F30" s="102">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="130">
+      <c r="J30" s="129">
         <v>215</v>
       </c>
-      <c r="M30" s="116">
+      <c r="M30" s="115">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="127" t="s">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B31" s="126" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="104">
+      <c r="C31" s="103">
         <v>4000</v>
       </c>
-      <c r="D31" s="104">
-        <v>0</v>
-      </c>
-      <c r="E31" s="125"/>
-      <c r="F31" s="103">
+      <c r="D31" s="103">
+        <v>0</v>
+      </c>
+      <c r="E31" s="124"/>
+      <c r="F31" s="102">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="116">
+      <c r="J31" s="115">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="127" t="s">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B32" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="104">
+      <c r="C32" s="103">
         <v>4000</v>
       </c>
-      <c r="D32" s="104">
-        <v>0</v>
-      </c>
-      <c r="E32" s="125"/>
-      <c r="F32" s="103">
+      <c r="D32" s="103">
+        <v>0</v>
+      </c>
+      <c r="E32" s="124"/>
+      <c r="F32" s="102">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="116">
+      <c r="J32" s="115">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="127" t="s">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B33" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="104">
+      <c r="C33" s="103">
         <v>4000</v>
       </c>
-      <c r="D33" s="104">
-        <v>0</v>
-      </c>
-      <c r="E33" s="125"/>
-      <c r="F33" s="103">
+      <c r="D33" s="103">
+        <v>0</v>
+      </c>
+      <c r="E33" s="124"/>
+      <c r="F33" s="102">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="116">
+      <c r="J33" s="115">
         <v>45</v>
       </c>
-      <c r="K33" s="129">
+      <c r="K33" s="128">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="127" t="s">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="126" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="104">
+      <c r="C34" s="103">
         <v>4000</v>
       </c>
-      <c r="D34" s="104">
-        <v>0</v>
-      </c>
-      <c r="E34" s="125"/>
-      <c r="F34" s="103">
+      <c r="D34" s="103">
+        <v>0</v>
+      </c>
+      <c r="E34" s="124"/>
+      <c r="F34" s="102">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="116">
+      <c r="J34" s="115">
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B35" s="127" t="s">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="126" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="104">
+      <c r="C35" s="103">
         <v>4000</v>
       </c>
-      <c r="D35" s="104">
-        <v>0</v>
-      </c>
-      <c r="E35" s="125"/>
-      <c r="F35" s="103">
+      <c r="D35" s="103">
+        <v>0</v>
+      </c>
+      <c r="E35" s="124"/>
+      <c r="F35" s="102">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="116">
+      <c r="J35" s="115">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="127" t="s">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="104">
+      <c r="C36" s="103">
         <v>4000</v>
       </c>
-      <c r="D36" s="104">
-        <v>0</v>
-      </c>
-      <c r="E36" s="125"/>
-      <c r="F36" s="103">
+      <c r="D36" s="103">
+        <v>0</v>
+      </c>
+      <c r="E36" s="124"/>
+      <c r="F36" s="102">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="116">
+      <c r="J36" s="115">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="127" t="s">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="126">
+      <c r="C37" s="125">
         <v>4000</v>
       </c>
-      <c r="D37" s="104">
-        <v>0</v>
-      </c>
-      <c r="E37" s="125"/>
-      <c r="F37" s="103">
+      <c r="D37" s="103">
+        <v>0</v>
+      </c>
+      <c r="E37" s="124"/>
+      <c r="F37" s="102">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="127" t="s">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="126">
+      <c r="C38" s="125">
         <v>4000</v>
       </c>
-      <c r="D38" s="126">
+      <c r="D38" s="125">
         <v>3500</v>
       </c>
-      <c r="E38" s="125" t="s">
+      <c r="E38" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="F38" s="103">
+      <c r="F38" s="102">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="128">
+      <c r="M38" s="127">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="127" t="s">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="126" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="126">
+      <c r="C39" s="125">
         <v>4000</v>
       </c>
-      <c r="D39" s="125"/>
-      <c r="E39" s="125"/>
-      <c r="F39" s="103">
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="102">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B40" s="127" t="s">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="126" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="126">
+      <c r="C40" s="125">
         <v>4000</v>
       </c>
-      <c r="D40" s="125"/>
-      <c r="E40" s="125"/>
-      <c r="F40" s="103">
+      <c r="D40" s="124"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="102">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="127" t="s">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="126">
+      <c r="C41" s="125">
         <v>4000</v>
       </c>
-      <c r="D41" s="125"/>
-      <c r="E41" s="125"/>
-      <c r="F41" s="103">
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="127" t="s">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="126" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="126">
-        <v>0</v>
-      </c>
-      <c r="D42" s="125"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="103">
+      <c r="C42" s="125">
+        <v>0</v>
+      </c>
+      <c r="D42" s="124"/>
+      <c r="E42" s="124"/>
+      <c r="F42" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="127" t="s">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="126" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="126">
-        <v>0</v>
-      </c>
-      <c r="D43" s="125"/>
-      <c r="E43" s="125"/>
-      <c r="F43" s="103">
+      <c r="C43" s="125">
+        <v>0</v>
+      </c>
+      <c r="D43" s="124"/>
+      <c r="E43" s="124"/>
+      <c r="F43" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="124" t="s">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="123">
-        <v>0</v>
-      </c>
-      <c r="D44" s="122"/>
-      <c r="E44" s="122"/>
-      <c r="F44" s="121">
+      <c r="C44" s="122">
+        <v>0</v>
+      </c>
+      <c r="D44" s="121"/>
+      <c r="E44" s="121"/>
+      <c r="F44" s="120">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B45" s="124" t="s">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="123" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="123">
-        <v>0</v>
-      </c>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="121">
+      <c r="C45" s="122">
+        <v>0</v>
+      </c>
+      <c r="D45" s="121"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="120">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B46" s="124" t="s">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="123" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="123">
-        <v>0</v>
-      </c>
-      <c r="D46" s="122"/>
-      <c r="E46" s="122"/>
-      <c r="F46" s="121">
+      <c r="C46" s="122">
+        <v>0</v>
+      </c>
+      <c r="D46" s="121"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="120">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="120" t="s">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="119" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="119">
+      <c r="C47" s="118">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="117">
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="116">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>

--- a/TUCUMAN 1061/Julio/tucuman Julio.xlsx
+++ b/TUCUMAN 1061/Julio/tucuman Julio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0403F209-D254-4EAB-ACB2-C41DC91A76D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97816A6A-0B30-40A2-A9EA-4BFF79CAA767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="166">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -561,6 +561,9 @@
   </si>
   <si>
     <t>subidos en juli 2025</t>
+  </si>
+  <si>
+    <t>Protocolizacion de acta volante - Diferencia de certificados por rubricas de libros</t>
   </si>
 </sst>
 </file>
@@ -583,7 +586,7 @@
     <numFmt numFmtId="175" formatCode="0.00000"/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,14 +833,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -895,7 +890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1326,21 +1321,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1381,7 +1361,7 @@
     <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1542,7 +1522,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1558,10 +1537,10 @@
     <xf numFmtId="1" fontId="25" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="37" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="36" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="38" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="37" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
@@ -1668,8 +1647,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="29" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1811,7 +1788,20 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2243,10 +2233,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="192">
+      <c r="E3" s="189">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="192"/>
+      <c r="F3" s="189"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2318,16 +2308,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="202" t="s">
+      <c r="A12" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="202"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="202"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="199"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
@@ -2351,7 +2341,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="189">
+      <c r="H14" s="238">
         <v>373590.5</v>
       </c>
     </row>
@@ -2365,7 +2355,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="189">
+      <c r="H15" s="238">
         <v>4030.28</v>
       </c>
     </row>
@@ -2379,7 +2369,7 @@
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
-      <c r="H16" s="182">
+      <c r="H16" s="181">
         <f>SUM(H13:H15)</f>
         <v>377620.78</v>
       </c>
@@ -2395,16 +2385,16 @@
       <c r="H17" s="43"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="203" t="s">
+      <c r="A18" s="200" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="204"/>
-      <c r="C18" s="204"/>
-      <c r="D18" s="204"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="204"/>
-      <c r="H18" s="205"/>
+      <c r="B18" s="201"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="201"/>
+      <c r="G18" s="201"/>
+      <c r="H18" s="202"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
@@ -2416,7 +2406,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="188">
+      <c r="H19" s="26">
         <v>177932.77</v>
       </c>
     </row>
@@ -2430,8 +2420,8 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="188">
-        <v>358054.16</v>
+      <c r="H20" s="26">
+        <v>355749.36</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2446,20 +2436,20 @@
       <c r="G21" s="22"/>
       <c r="H21" s="27">
         <f>SUM(H19:H20)</f>
-        <v>535986.92999999993</v>
+        <v>533682.13</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="206" t="s">
+      <c r="A22" s="203" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="206"/>
-      <c r="C22" s="206"/>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="206"/>
-      <c r="H22" s="206"/>
+      <c r="B22" s="203"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="203"/>
       <c r="J22" s="26"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2472,7 +2462,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="188">
+      <c r="H23" s="26">
         <v>42645</v>
       </c>
       <c r="I23" s="14"/>
@@ -2488,7 +2478,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="188">
+      <c r="H24" s="26">
         <v>49340</v>
       </c>
       <c r="I24" s="14"/>
@@ -2504,7 +2494,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="188">
+      <c r="H25" s="26">
         <v>65000</v>
       </c>
     </row>
@@ -2524,16 +2514,16 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="203" t="s">
+      <c r="A27" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="204"/>
-      <c r="C27" s="204"/>
-      <c r="D27" s="204"/>
-      <c r="E27" s="204"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="204"/>
-      <c r="H27" s="205"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="201"/>
+      <c r="F27" s="201"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="202"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
@@ -2560,7 +2550,7 @@
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
-      <c r="H29" s="237">
+      <c r="H29" s="239">
         <v>66600</v>
       </c>
       <c r="I29" s="44"/>
@@ -2579,16 +2569,16 @@
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="203" t="s">
+      <c r="A31" s="200" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="204"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="204"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="204"/>
-      <c r="H31" s="205"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="201"/>
+      <c r="F31" s="201"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
@@ -2613,7 +2603,7 @@
       <c r="G33" s="31"/>
       <c r="H33" s="32">
         <f>H16+H21+H26+H29+H32</f>
-        <v>1137192.71</v>
+        <v>1134887.9100000001</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
@@ -2629,103 +2619,107 @@
       <c r="H34" s="48"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="193" t="s">
+      <c r="A35" s="190" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="195"/>
-      <c r="I35" s="168"/>
-      <c r="K35" s="168"/>
+      <c r="B35" s="191"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="167"/>
+      <c r="K35" s="167"/>
     </row>
     <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="196"/>
-      <c r="B36" s="197"/>
-      <c r="C36" s="197"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="197"/>
-      <c r="F36" s="197"/>
-      <c r="G36" s="197"/>
-      <c r="H36" s="198"/>
+      <c r="A36" s="193"/>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+      <c r="G36" s="194"/>
+      <c r="H36" s="195"/>
     </row>
     <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="207"/>
-      <c r="B37" s="208"/>
-      <c r="C37" s="208"/>
-      <c r="D37" s="208"/>
-      <c r="E37" s="208"/>
-      <c r="F37" s="208"/>
-      <c r="G37" s="209"/>
-      <c r="H37" s="33"/>
+      <c r="A37" s="204" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="205"/>
+      <c r="C37" s="205"/>
+      <c r="D37" s="205"/>
+      <c r="E37" s="205"/>
+      <c r="F37" s="205"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="236">
+        <v>470300</v>
+      </c>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="207"/>
-      <c r="B38" s="208"/>
-      <c r="C38" s="208"/>
-      <c r="D38" s="208"/>
-      <c r="E38" s="208"/>
-      <c r="F38" s="208"/>
-      <c r="G38" s="209"/>
+      <c r="A38" s="204"/>
+      <c r="B38" s="205"/>
+      <c r="C38" s="205"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="205"/>
+      <c r="F38" s="205"/>
+      <c r="G38" s="206"/>
       <c r="H38" s="33"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="210"/>
-      <c r="B39" s="211"/>
-      <c r="C39" s="211"/>
-      <c r="D39" s="211"/>
-      <c r="E39" s="211"/>
-      <c r="F39" s="211"/>
-      <c r="G39" s="212"/>
+      <c r="A39" s="207"/>
+      <c r="B39" s="208"/>
+      <c r="C39" s="208"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="209"/>
       <c r="H39" s="33"/>
     </row>
     <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="213" t="s">
+      <c r="A40" s="210" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="214"/>
-      <c r="C40" s="214"/>
-      <c r="D40" s="214"/>
-      <c r="E40" s="214"/>
-      <c r="F40" s="214"/>
-      <c r="G40" s="215"/>
+      <c r="B40" s="211"/>
+      <c r="C40" s="211"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="212"/>
       <c r="H40" s="34">
         <f>SUM(H37:H39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
+        <v>470300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="234"/>
+      <c r="B41" s="234"/>
+      <c r="C41" s="234"/>
+      <c r="D41" s="234"/>
+      <c r="E41" s="234"/>
+      <c r="F41" s="234"/>
+      <c r="G41" s="234"/>
+      <c r="H41" s="235"/>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H42" s="19"/>
       <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="190" t="s">
+      <c r="A43" s="187" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="190"/>
-      <c r="C43" s="190"/>
-      <c r="D43" s="190"/>
-      <c r="E43" s="190"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
+      <c r="B43" s="187"/>
+      <c r="C43" s="187"/>
+      <c r="D43" s="187"/>
+      <c r="E43" s="187"/>
+      <c r="F43" s="187"/>
+      <c r="G43" s="187"/>
       <c r="H43" s="32">
         <f>+H33+H34</f>
-        <v>1137192.71</v>
-      </c>
-      <c r="J43" s="168"/>
+        <v>1134887.9100000001</v>
+      </c>
+      <c r="J43" s="167"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="19"/>
@@ -2749,7 +2743,7 @@
       <c r="G45" s="31"/>
       <c r="H45" s="35">
         <f>H40</f>
-        <v>0</v>
+        <v>470300</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2763,29 +2757,29 @@
       <c r="H46" s="19"/>
     </row>
     <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="199" t="s">
+      <c r="A47" s="196" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="200"/>
-      <c r="C47" s="200"/>
-      <c r="D47" s="200"/>
-      <c r="E47" s="200"/>
-      <c r="F47" s="200"/>
-      <c r="G47" s="200"/>
-      <c r="H47" s="201"/>
+      <c r="B47" s="197"/>
+      <c r="C47" s="197"/>
+      <c r="D47" s="197"/>
+      <c r="E47" s="197"/>
+      <c r="F47" s="197"/>
+      <c r="G47" s="197"/>
+      <c r="H47" s="198"/>
     </row>
     <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="191" t="s">
+      <c r="A48" s="188" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="191"/>
-      <c r="C48" s="191"/>
-      <c r="D48" s="191"/>
-      <c r="E48" s="191"/>
-      <c r="F48" s="191"/>
-      <c r="G48" s="191"/>
+      <c r="B48" s="188"/>
+      <c r="C48" s="188"/>
+      <c r="D48" s="188"/>
+      <c r="E48" s="188"/>
+      <c r="F48" s="188"/>
+      <c r="G48" s="188"/>
       <c r="H48" s="41">
-        <v>1108407.9439299698</v>
+        <v>1958258.8766773101</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2800,7 +2794,7 @@
       <c r="G49" s="37"/>
       <c r="H49" s="45">
         <f>Planilla!I31</f>
-        <v>2672781.3927473403</v>
+        <v>1480247.3410500004</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2815,7 +2809,7 @@
       <c r="G50" s="37"/>
       <c r="H50" s="38">
         <f>-(H33+H40)</f>
-        <v>-1137192.71</v>
+        <v>-1605187.9100000001</v>
       </c>
       <c r="J50" s="15"/>
     </row>
@@ -2831,7 +2825,7 @@
       <c r="G51" s="40"/>
       <c r="H51" s="49">
         <f>SUM(H48:H50)</f>
-        <v>2643996.6266773101</v>
+        <v>1833318.3077273103</v>
       </c>
     </row>
   </sheetData>
@@ -2883,39 +2877,39 @@
     <col min="13" max="13" width="10.28515625" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="219" t="str">
+      <c r="A1" s="216" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: JULIO </v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="220"/>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="221"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="218"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="92"/>
-      <c r="C2" s="184">
-        <v>1822930.46</v>
+      <c r="C2" s="183">
+        <v>1134887.9100000001</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
@@ -2927,8 +2921,8 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="D3" s="184">
-        <v>358698.61</v>
+      <c r="D3" s="183">
+        <v>355749.36</v>
       </c>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
@@ -2948,21 +2942,21 @@
       <c r="I4" s="56"/>
       <c r="J4" s="56"/>
       <c r="L4" s="90"/>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="218"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="215"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="227">
+      <c r="C5" s="224">
         <f>D3</f>
-        <v>358698.61</v>
-      </c>
-      <c r="D5" s="227"/>
+        <v>355749.36</v>
+      </c>
+      <c r="D5" s="224"/>
       <c r="E5" s="13"/>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
@@ -2990,11 +2984,11 @@
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="88"/>
       <c r="B7" s="87"/>
-      <c r="C7" s="227">
+      <c r="C7" s="224">
         <f>C2-D3</f>
-        <v>1464231.85</v>
-      </c>
-      <c r="D7" s="227"/>
+        <v>779138.55000000016</v>
+      </c>
+      <c r="D7" s="224"/>
       <c r="E7" s="89"/>
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
@@ -3023,8 +3017,10 @@
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="86"/>
       <c r="B9" s="85"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
+      <c r="C9" s="237">
+        <v>470300</v>
+      </c>
+      <c r="D9" s="237"/>
       <c r="E9" s="84"/>
       <c r="F9" s="83"/>
       <c r="G9" s="82"/>
@@ -3097,29 +3093,29 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="175" t="s">
+      <c r="A11" s="174" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="176"/>
-      <c r="C11" s="177" t="s">
+      <c r="B11" s="175"/>
+      <c r="C11" s="176" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="178" t="s">
+      <c r="D11" s="177" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="164"/>
-      <c r="F11" s="179">
+      <c r="E11" s="163"/>
+      <c r="F11" s="178">
         <v>7.9</v>
       </c>
       <c r="G11" s="67">
-        <v>118500.00000000001</v>
+        <v>144011.50634000002</v>
       </c>
       <c r="H11" s="67">
         <v>0</v>
       </c>
       <c r="I11" s="67">
         <f>G11</f>
-        <v>118500.00000000001</v>
+        <v>144011.50634000002</v>
       </c>
       <c r="J11" s="67" t="e">
         <f>C8*F11/100</f>
@@ -3130,182 +3126,182 @@
         <v>0</v>
       </c>
       <c r="L11" s="67"/>
-      <c r="M11" s="180">
+      <c r="M11" s="179">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="180">
+      <c r="N11" s="179">
         <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
         <v>0</v>
       </c>
       <c r="O11" s="67">
         <f>C$7*F11/100</f>
-        <v>115674.31615000003</v>
+        <v>61551.945450000021</v>
       </c>
       <c r="P11" s="67">
-        <f t="shared" ref="P11:P30" si="2">C$9*F11/100</f>
-        <v>0</v>
+        <f>C$9*F11/100</f>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q11" s="67">
         <f>C$5*F11/100</f>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R11" s="180">
-        <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
-        <v>144011.50634000002</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R11" s="179">
+        <f t="shared" ref="R11:R29" si="2">O11+N11+P11+Q11</f>
+        <v>126809.84489000001</v>
       </c>
       <c r="U11" s="93" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="169" t="s">
+      <c r="A12" s="168" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="162"/>
-      <c r="C12" s="170" t="s">
+      <c r="B12" s="161"/>
+      <c r="C12" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="171" t="s">
+      <c r="D12" s="170" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="172"/>
-      <c r="F12" s="173">
+      <c r="E12" s="171"/>
+      <c r="F12" s="172">
         <v>7.9</v>
       </c>
-      <c r="G12" s="160">
-        <v>118500.00000000001</v>
-      </c>
-      <c r="H12" s="160">
+      <c r="G12" s="159">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="H12" s="159">
         <v>0</v>
       </c>
       <c r="I12" s="67">
         <f>G12</f>
-        <v>118500.00000000001</v>
-      </c>
-      <c r="J12" s="160" t="e">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="J12" s="159" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="160">
+      <c r="K12" s="159">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="160"/>
-      <c r="M12" s="166">
-        <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="166">
+      <c r="L12" s="159"/>
+      <c r="M12" s="165">
+        <f t="shared" ref="M12:M29" si="3">(K12+L12)*3%</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="165">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="160">
-        <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P12" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="O12" s="159">
+        <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P12" s="67">
+        <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q12" s="67">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R12" s="166">
-        <f t="shared" si="3"/>
-        <v>144011.50634000002</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R12" s="165">
+        <f t="shared" si="2"/>
+        <v>126809.84489000001</v>
       </c>
       <c r="U12" s="94" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="161" t="s">
+      <c r="A13" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="162"/>
+      <c r="B13" s="161"/>
       <c r="C13" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="163" t="s">
+      <c r="D13" s="162" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="164" t="s">
+      <c r="E13" s="163" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="165">
+      <c r="F13" s="164">
         <v>7.9</v>
       </c>
       <c r="G13" s="67">
-        <v>646653.19954050251</v>
-      </c>
-      <c r="H13" s="160">
+        <v>144004.50186671762</v>
+      </c>
+      <c r="H13" s="159">
         <v>0</v>
       </c>
       <c r="I13" s="67">
-        <f>300000+133890+212770</f>
-        <v>646660</v>
-      </c>
-      <c r="J13" s="160" t="e">
+        <f>144005</f>
+        <v>144005</v>
+      </c>
+      <c r="J13" s="159" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="160">
+      <c r="K13" s="159">
         <f t="shared" si="0"/>
-        <v>-6.8004594974918291</v>
-      </c>
-      <c r="L13" s="160"/>
-      <c r="M13" s="166">
+        <v>-0.49813328238087706</v>
+      </c>
+      <c r="L13" s="159"/>
+      <c r="M13" s="165">
+        <f t="shared" si="3"/>
+        <v>-1.4943998471426311E-2</v>
+      </c>
+      <c r="N13" s="165">
+        <f t="shared" si="1"/>
+        <v>-0.51307728085230342</v>
+      </c>
+      <c r="O13" s="159">
         <f t="shared" si="4"/>
-        <v>-0.20401378492475486</v>
-      </c>
-      <c r="N13" s="166">
-        <f t="shared" si="1"/>
-        <v>-7.0044732824165843</v>
-      </c>
-      <c r="O13" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P13" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P13" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q13" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R13" s="166">
-        <f t="shared" si="3"/>
-        <v>144004.50186671762</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R13" s="165">
+        <f t="shared" si="2"/>
+        <v>126809.33181271916</v>
       </c>
       <c r="U13" s="94" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="110" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="75"/>
       <c r="C14" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="157" t="s">
+      <c r="D14" s="156" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="114"/>
+      <c r="E14" s="113"/>
       <c r="F14" s="96">
         <v>7.9</v>
       </c>
-      <c r="G14" s="159">
-        <v>118497.94000000002</v>
+      <c r="G14" s="158">
+        <v>144011.50634000002</v>
       </c>
       <c r="H14" s="74"/>
       <c r="I14" s="67">
         <f>G14</f>
-        <v>118497.94000000002</v>
+        <v>144011.50634000002</v>
       </c>
       <c r="J14" s="65" t="e">
         <f>C8*F14/100</f>
@@ -3317,7 +3313,7 @@
       </c>
       <c r="L14" s="66"/>
       <c r="M14" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="64">
@@ -3325,175 +3321,172 @@
         <v>0</v>
       </c>
       <c r="O14" s="65">
+        <f t="shared" si="4"/>
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P14" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P14" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q14" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
+        <v>28104.19944</v>
       </c>
       <c r="R14" s="64">
-        <f t="shared" si="3"/>
-        <v>144011.50634000002</v>
+        <f t="shared" si="2"/>
+        <v>126809.84489000001</v>
       </c>
       <c r="U14" s="94" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="110" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="112" t="s">
+      <c r="D15" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="113"/>
       <c r="F15" s="96">
         <v>7.9</v>
       </c>
       <c r="G15" s="72">
-        <v>229710.6036811966</v>
+        <v>144011.22511827253</v>
       </c>
       <c r="H15" s="74">
         <v>0</v>
       </c>
-      <c r="I15" s="67">
-        <f>237847-G27</f>
-        <v>229710.876712</v>
-      </c>
+      <c r="I15" s="67"/>
       <c r="J15" s="65" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K15" s="65">
         <f t="shared" si="0"/>
-        <v>-0.27303080339333974</v>
+        <v>144011.22511827253</v>
       </c>
       <c r="L15" s="65"/>
       <c r="M15" s="64">
-        <f t="shared" si="4"/>
-        <v>-8.190924101800192E-3</v>
+        <f t="shared" si="3"/>
+        <v>4320.3367535481757</v>
       </c>
       <c r="N15" s="64">
         <f t="shared" si="1"/>
-        <v>-0.28122172749513991</v>
+        <v>148331.56187182071</v>
       </c>
       <c r="O15" s="65">
+        <f t="shared" si="4"/>
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P15" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P15" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q15" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
+        <v>28104.19944</v>
       </c>
       <c r="R15" s="64">
-        <f t="shared" si="3"/>
-        <v>144011.22511827253</v>
+        <f t="shared" si="2"/>
+        <v>275141.40676182072</v>
       </c>
       <c r="U15" s="94" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="162"/>
+      <c r="B16" s="161"/>
       <c r="C16" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="163" t="s">
+      <c r="D16" s="162" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="164"/>
-      <c r="F16" s="165">
+      <c r="E16" s="163"/>
+      <c r="F16" s="164">
         <v>7.9</v>
       </c>
       <c r="G16" s="67">
-        <v>824894.30490492634</v>
-      </c>
-      <c r="H16" s="160">
+        <v>144011.728561717</v>
+      </c>
+      <c r="H16" s="159">
         <v>0</v>
       </c>
       <c r="I16" s="67">
-        <f>888825-I28</f>
-        <v>824894.08915568655</v>
-      </c>
-      <c r="J16" s="160" t="e">
+        <f>154847-I28</f>
+        <v>144011.68431000001</v>
+      </c>
+      <c r="J16" s="159" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="160">
+      <c r="K16" s="159">
         <f t="shared" si="0"/>
-        <v>0.21574923978187144</v>
-      </c>
-      <c r="L16" s="160"/>
-      <c r="M16" s="166">
+        <v>4.4251716986764222E-2</v>
+      </c>
+      <c r="L16" s="159"/>
+      <c r="M16" s="165">
+        <f t="shared" si="3"/>
+        <v>1.3275515096029266E-3</v>
+      </c>
+      <c r="N16" s="165">
+        <f t="shared" si="1"/>
+        <v>4.5579268496367148E-2</v>
+      </c>
+      <c r="O16" s="159">
         <f t="shared" si="4"/>
-        <v>6.4724771934561425E-3</v>
-      </c>
-      <c r="N16" s="166">
-        <f t="shared" si="1"/>
-        <v>0.22222171697532758</v>
-      </c>
-      <c r="O16" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P16" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P16" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q16" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R16" s="166">
-        <f t="shared" si="3"/>
-        <v>144011.728561717</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R16" s="165">
+        <f t="shared" si="2"/>
+        <v>126809.89046926852</v>
       </c>
       <c r="U16" s="94" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="110" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="71"/>
       <c r="C17" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="112" t="s">
+      <c r="D17" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="114" t="s">
+      <c r="E17" s="113" t="s">
         <v>146</v>
       </c>
       <c r="F17" s="96">
         <v>7.9</v>
       </c>
       <c r="G17" s="72">
-        <v>145557.97902211564</v>
+        <v>152395.81171941914</v>
       </c>
       <c r="H17" s="65">
         <v>0</v>
       </c>
       <c r="I17" s="67">
-        <f>145554-I23</f>
-        <v>137417.876712</v>
+        <f>163231-I23</f>
+        <v>152395.68431000001</v>
       </c>
       <c r="J17" s="65" t="e">
         <f>C8*F17/100</f>
@@ -3501,185 +3494,184 @@
       </c>
       <c r="K17" s="65">
         <f t="shared" si="0"/>
-        <v>8140.1023101156461</v>
+        <v>0.12740941913216375</v>
       </c>
       <c r="L17" s="65"/>
       <c r="M17" s="64">
-        <f t="shared" si="4"/>
-        <v>244.20306930346936</v>
+        <f t="shared" si="3"/>
+        <v>3.8222825739649123E-3</v>
       </c>
       <c r="N17" s="64">
         <f t="shared" si="1"/>
-        <v>8384.3053794191146</v>
+        <v>0.13123170170612866</v>
       </c>
       <c r="O17" s="65">
+        <f t="shared" si="4"/>
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P17" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P17" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q17" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
+        <v>28104.19944</v>
       </c>
       <c r="R17" s="64">
-        <f t="shared" si="3"/>
-        <v>152395.81171941914</v>
+        <f t="shared" si="2"/>
+        <v>126809.97612170172</v>
       </c>
       <c r="U17" s="94" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="161" t="s">
+      <c r="A18" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="162"/>
+      <c r="B18" s="161"/>
       <c r="C18" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="163" t="s">
+      <c r="D18" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="164" t="s">
+      <c r="E18" s="163" t="s">
         <v>147</v>
       </c>
-      <c r="F18" s="165">
+      <c r="F18" s="164">
         <v>7.9</v>
       </c>
       <c r="G18" s="67">
-        <v>313538.37315287697</v>
-      </c>
-      <c r="H18" s="160">
+        <v>466956.0306874633</v>
+      </c>
+      <c r="H18" s="159">
         <v>0</v>
       </c>
       <c r="I18" s="67"/>
-      <c r="J18" s="160" t="e">
+      <c r="J18" s="159" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="160">
+      <c r="K18" s="159">
         <f t="shared" si="0"/>
-        <v>313538.37315287697</v>
-      </c>
-      <c r="L18" s="160"/>
-      <c r="M18" s="166">
+        <v>466956.0306874633</v>
+      </c>
+      <c r="L18" s="159"/>
+      <c r="M18" s="165">
+        <f t="shared" si="3"/>
+        <v>14008.680920623898</v>
+      </c>
+      <c r="N18" s="165">
+        <f t="shared" si="1"/>
+        <v>480964.71160808718</v>
+      </c>
+      <c r="O18" s="159">
         <f t="shared" si="4"/>
-        <v>9406.1511945863094</v>
-      </c>
-      <c r="N18" s="166">
-        <f t="shared" si="1"/>
-        <v>322944.52434746327</v>
-      </c>
-      <c r="O18" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P18" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P18" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q18" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R18" s="166">
-        <f t="shared" si="3"/>
-        <v>466956.0306874633</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R18" s="165">
+        <f t="shared" si="2"/>
+        <v>607774.55649808713</v>
       </c>
       <c r="U18" s="94" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="161" t="s">
+      <c r="A19" s="160" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="162"/>
+      <c r="B19" s="161"/>
       <c r="C19" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="163" t="s">
+      <c r="D19" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="165">
+      <c r="E19" s="163"/>
+      <c r="F19" s="164">
         <v>7.9</v>
       </c>
       <c r="G19" s="67">
-        <v>117558.69960956796</v>
-      </c>
-      <c r="H19" s="160">
+        <v>145945.22753571003</v>
+      </c>
+      <c r="H19" s="159">
         <v>0</v>
       </c>
       <c r="I19" s="67">
-        <f>116620</f>
-        <v>116620</v>
-      </c>
-      <c r="J19" s="160" t="e">
+        <v>146000</v>
+      </c>
+      <c r="J19" s="159" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="160">
+      <c r="K19" s="159">
         <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
-        <v>938.69960956796422</v>
-      </c>
-      <c r="L19" s="160">
+        <v>-54.77246428997023</v>
+      </c>
+      <c r="L19" s="159">
         <f>G19-I19</f>
-        <v>938.69960956796422</v>
-      </c>
-      <c r="M19" s="166">
+        <v>-54.77246428997023</v>
+      </c>
+      <c r="M19" s="165">
+        <f t="shared" si="3"/>
+        <v>-3.2863478573982139</v>
+      </c>
+      <c r="N19" s="165">
+        <f t="shared" si="1"/>
+        <v>-112.83127643733867</v>
+      </c>
+      <c r="O19" s="159">
         <f t="shared" si="4"/>
-        <v>56.321976574077851</v>
-      </c>
-      <c r="N19" s="166">
-        <f t="shared" si="1"/>
-        <v>1933.7211957100062</v>
-      </c>
-      <c r="O19" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P19" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P19" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q19" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R19" s="166">
-        <f t="shared" si="3"/>
-        <v>145945.22753571003</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R19" s="165">
+        <f t="shared" si="2"/>
+        <v>126697.01361356268</v>
       </c>
       <c r="U19" s="94" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="110" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="71"/>
       <c r="C20" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="112" t="s">
+      <c r="D20" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="114"/>
+      <c r="E20" s="113"/>
       <c r="F20" s="96">
         <v>7.9</v>
       </c>
       <c r="G20" s="72">
-        <v>147005.20617134054</v>
+        <v>144011.50634000002</v>
       </c>
       <c r="H20" s="65"/>
       <c r="I20" s="67">
         <f>G20</f>
-        <v>147005.20617134054</v>
+        <v>144011.50634000002</v>
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="65">
@@ -3688,7 +3680,7 @@
       </c>
       <c r="L20" s="65"/>
       <c r="M20" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20" s="64">
@@ -3696,164 +3688,164 @@
         <v>0</v>
       </c>
       <c r="O20" s="65">
+        <f t="shared" si="4"/>
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P20" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P20" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q20" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
+        <v>28104.19944</v>
       </c>
       <c r="R20" s="64">
-        <f t="shared" si="3"/>
-        <v>144011.50634000002</v>
+        <f t="shared" si="2"/>
+        <v>126809.84489000001</v>
       </c>
       <c r="U20" s="94" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="161" t="s">
+      <c r="A21" s="160" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="162"/>
+      <c r="B21" s="161"/>
       <c r="C21" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="163" t="s">
+      <c r="D21" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="164" t="s">
+      <c r="E21" s="163" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="165">
+      <c r="F21" s="164">
         <v>7.9</v>
       </c>
       <c r="G21" s="67">
-        <v>118500.17984677525</v>
-      </c>
-      <c r="H21" s="160"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="160">
+        <v>266066.69158217852</v>
+      </c>
+      <c r="H21" s="159"/>
+      <c r="I21" s="67">
+        <f>285283-I24</f>
+        <v>266067.47732335998</v>
+      </c>
+      <c r="J21" s="159"/>
+      <c r="K21" s="159">
         <f t="shared" si="7"/>
-        <v>118500.17984677525</v>
-      </c>
-      <c r="L21" s="160"/>
-      <c r="M21" s="166">
+        <v>-0.78574118146207184</v>
+      </c>
+      <c r="L21" s="159"/>
+      <c r="M21" s="165">
+        <f t="shared" si="3"/>
+        <v>-2.3572235443862156E-2</v>
+      </c>
+      <c r="N21" s="165">
+        <f t="shared" si="8"/>
+        <v>-0.80931341690593395</v>
+      </c>
+      <c r="O21" s="159">
         <f t="shared" si="4"/>
-        <v>3555.0053954032574</v>
-      </c>
-      <c r="N21" s="166">
-        <f t="shared" si="8"/>
-        <v>122055.18524217852</v>
-      </c>
-      <c r="O21" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P21" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P21" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q21" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R21" s="166">
-        <f t="shared" si="3"/>
-        <v>266066.69158217852</v>
+        <v>28104.19944</v>
+      </c>
+      <c r="R21" s="165">
+        <f t="shared" si="2"/>
+        <v>126809.03557658312</v>
       </c>
       <c r="U21" s="94" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="161" t="s">
+      <c r="A22" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="162"/>
+      <c r="B22" s="161"/>
       <c r="C22" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="163" t="s">
+      <c r="D22" s="162" t="s">
         <v>154</v>
       </c>
-      <c r="E22" s="164" t="s">
+      <c r="E22" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="F22" s="165">
+      <c r="F22" s="164">
         <v>7.9</v>
       </c>
       <c r="G22" s="67">
-        <v>118500.00000000001</v>
-      </c>
-      <c r="H22" s="160"/>
-      <c r="I22" s="67">
-        <f>G22</f>
-        <v>118500.00000000001</v>
-      </c>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="H22" s="159"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="159">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="160"/>
-      <c r="M22" s="166">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="L22" s="159"/>
+      <c r="M22" s="165">
+        <f t="shared" si="3"/>
+        <v>4320.3451902000006</v>
+      </c>
+      <c r="N22" s="165">
+        <f t="shared" si="8"/>
+        <v>148331.85153020002</v>
+      </c>
+      <c r="O22" s="159">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="166">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="160">
+        <v>61551.945450000021</v>
+      </c>
+      <c r="P22" s="67">
         <f t="shared" si="5"/>
-        <v>115674.31615000003</v>
-      </c>
-      <c r="P22" s="160">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37153.699999999997</v>
       </c>
       <c r="Q22" s="67">
         <f t="shared" si="6"/>
-        <v>28337.190189999998</v>
-      </c>
-      <c r="R22" s="166">
-        <f t="shared" si="3"/>
-        <v>144011.50634000002</v>
-      </c>
-      <c r="S22" s="181"/>
+        <v>28104.19944</v>
+      </c>
+      <c r="R22" s="165">
+        <f t="shared" si="2"/>
+        <v>275141.69642020005</v>
+      </c>
+      <c r="S22" s="180"/>
       <c r="U22" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="111"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="71"/>
       <c r="C23" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="113" t="str">
+      <c r="D23" s="112" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="114" t="s">
+      <c r="E23" s="113" t="s">
         <v>146</v>
       </c>
       <c r="F23" s="96">
         <v>0.74</v>
       </c>
       <c r="G23" s="72">
-        <v>8136.1232879999998</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="H23" s="65"/>
       <c r="I23" s="67">
         <f>G23</f>
-        <v>8136.1232879999998</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65">
@@ -3862,7 +3854,7 @@
       </c>
       <c r="L23" s="65"/>
       <c r="M23" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="64">
@@ -3870,98 +3862,101 @@
         <v>0</v>
       </c>
       <c r="O23" s="65">
+        <f t="shared" si="4"/>
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P23" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P23" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3480.22</v>
       </c>
       <c r="Q23" s="65"/>
       <c r="R23" s="64">
-        <f t="shared" si="3"/>
-        <v>10835.315690000001</v>
+        <f t="shared" si="2"/>
+        <v>9245.8452700000016</v>
       </c>
       <c r="U23" s="94" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="161"/>
-      <c r="B24" s="162"/>
+      <c r="A24" s="160"/>
+      <c r="B24" s="161"/>
       <c r="C24" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="167" t="str">
+      <c r="D24" s="166" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="163" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="165">
+      <c r="F24" s="164">
         <v>0.74</v>
       </c>
       <c r="G24" s="67">
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="H24" s="160"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="160"/>
-      <c r="K24" s="160">
+        <v>19215.522676640001</v>
+      </c>
+      <c r="H24" s="159"/>
+      <c r="I24" s="67">
+        <f>G24</f>
+        <v>19215.522676640001</v>
+      </c>
+      <c r="J24" s="159"/>
+      <c r="K24" s="159">
         <f t="shared" si="7"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="L24" s="160"/>
-      <c r="M24" s="166">
+        <v>0</v>
+      </c>
+      <c r="L24" s="159"/>
+      <c r="M24" s="165">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="165">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="159">
         <f t="shared" si="4"/>
-        <v>244.08369863999999</v>
-      </c>
-      <c r="N24" s="166">
-        <f t="shared" si="8"/>
-        <v>8380.2069866399997</v>
-      </c>
-      <c r="O24" s="160">
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P24" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P24" s="160">
+        <v>3480.22</v>
+      </c>
+      <c r="Q24" s="159">
+        <f>'Calculo Servicios  (2)'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="165">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="160">
-        <f>'Calculo Servicios  (2)'!H22</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="166">
-        <f t="shared" si="3"/>
-        <v>19215.522676640001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="U24" s="94" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="111"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="71"/>
       <c r="C25" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="113" t="str">
+      <c r="D25" s="112" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="113"/>
+      <c r="E25" s="112"/>
       <c r="F25" s="96">
         <v>0.74</v>
       </c>
       <c r="G25" s="72">
-        <v>8136.1232879999998</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="H25" s="65"/>
       <c r="I25" s="67">
         <f t="shared" ref="I25" si="9">G25</f>
-        <v>8136.1232879999998</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="65">
@@ -3970,7 +3965,7 @@
       </c>
       <c r="L25" s="65"/>
       <c r="M25" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N25" s="64">
@@ -3978,169 +3973,166 @@
         <v>0</v>
       </c>
       <c r="O25" s="65">
+        <f t="shared" si="4"/>
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P25" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P25" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3480.22</v>
       </c>
       <c r="Q25" s="65">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
       <c r="R25" s="64">
-        <f t="shared" si="3"/>
-        <v>10835.315690000001</v>
+        <f t="shared" si="2"/>
+        <v>9245.8452700000016</v>
       </c>
       <c r="U25" s="94" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="161"/>
-      <c r="B26" s="158"/>
+      <c r="A26" s="160"/>
+      <c r="B26" s="157"/>
       <c r="C26" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="167" t="str">
+      <c r="D26" s="166" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="164" t="s">
+      <c r="E26" s="163" t="s">
         <v>147</v>
       </c>
-      <c r="F26" s="165">
+      <c r="F26" s="164">
         <v>0.74</v>
       </c>
       <c r="G26" s="67">
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="H26" s="160">
+        <v>19215.522676640001</v>
+      </c>
+      <c r="H26" s="159">
         <v>0</v>
       </c>
       <c r="I26" s="67"/>
-      <c r="J26" s="160" t="e">
+      <c r="J26" s="159" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="160">
+      <c r="K26" s="159">
         <f t="shared" si="7"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="L26" s="160"/>
-      <c r="M26" s="166">
+        <v>19215.522676640001</v>
+      </c>
+      <c r="L26" s="159"/>
+      <c r="M26" s="165">
+        <f t="shared" si="3"/>
+        <v>576.46568029920002</v>
+      </c>
+      <c r="N26" s="165">
+        <f t="shared" si="8"/>
+        <v>19791.9883569392</v>
+      </c>
+      <c r="O26" s="159">
         <f t="shared" si="4"/>
-        <v>244.08369863999999</v>
-      </c>
-      <c r="N26" s="166">
-        <f t="shared" si="8"/>
-        <v>8380.2069866399997</v>
-      </c>
-      <c r="O26" s="160">
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P26" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P26" s="160">
+        <v>3480.22</v>
+      </c>
+      <c r="Q26" s="159">
+        <f>'Calculo Servicios  (2)'!H24</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="165">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="160">
-        <f>'Calculo Servicios  (2)'!H24</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="166">
-        <f t="shared" si="3"/>
-        <v>19215.522676640001</v>
+        <v>29037.833626939202</v>
       </c>
       <c r="U26" s="94" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="111"/>
+      <c r="A27" s="110"/>
       <c r="B27" s="71"/>
       <c r="C27" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="113" t="str">
+      <c r="D27" s="112" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="113"/>
+      <c r="E27" s="112"/>
       <c r="F27" s="96">
         <v>0.74</v>
       </c>
       <c r="G27" s="72">
-        <v>8136.1232879999998</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="H27" s="65">
         <v>0</v>
       </c>
-      <c r="I27" s="67">
-        <f>G27</f>
-        <v>8136.1232879999998</v>
-      </c>
+      <c r="I27" s="67"/>
       <c r="J27" s="65" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K27" s="65">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="L27" s="65"/>
       <c r="M27" s="64">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>325.05947070000002</v>
       </c>
       <c r="N27" s="64">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11160.375160700001</v>
       </c>
       <c r="O27" s="65">
+        <f t="shared" si="4"/>
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P27" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P27" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3480.22</v>
       </c>
       <c r="Q27" s="65">
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
       <c r="R27" s="64">
-        <f t="shared" si="3"/>
-        <v>10835.315690000001</v>
+        <f t="shared" si="2"/>
+        <v>20406.220430700003</v>
       </c>
       <c r="U27" s="94" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="185"/>
-      <c r="B28" s="186"/>
+      <c r="A28" s="184"/>
+      <c r="B28" s="185"/>
       <c r="C28" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="167" t="str">
+      <c r="D28" s="166" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="164"/>
-      <c r="F28" s="187">
+      <c r="E28" s="163"/>
+      <c r="F28" s="186">
         <v>0.74</v>
       </c>
       <c r="G28" s="67">
-        <v>63930.91084431341</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="H28" s="67">
         <v>0</v>
       </c>
       <c r="I28" s="67">
         <f>G28</f>
-        <v>63930.91084431341</v>
+        <v>10835.315690000001</v>
       </c>
       <c r="J28" s="67">
         <v>0</v>
@@ -4150,92 +4142,89 @@
         <v>0</v>
       </c>
       <c r="L28" s="67"/>
-      <c r="M28" s="180">
+      <c r="M28" s="179">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="67">
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P28" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P28" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3480.22</v>
       </c>
       <c r="Q28" s="67">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="180">
-        <f t="shared" si="3"/>
-        <v>10835.315690000001</v>
+      <c r="R28" s="179">
+        <f t="shared" si="2"/>
+        <v>9245.8452700000016</v>
       </c>
       <c r="U28" s="94" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="161"/>
-      <c r="B29" s="174"/>
+      <c r="A29" s="160"/>
+      <c r="B29" s="173"/>
       <c r="C29" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="167" t="str">
+      <c r="D29" s="166" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="164" t="s">
+      <c r="E29" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="F29" s="183">
+      <c r="F29" s="182">
         <v>0.74</v>
       </c>
       <c r="G29" s="67">
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="H29" s="160">
-        <v>0</v>
-      </c>
-      <c r="I29" s="67">
-        <f>G29</f>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="J29" s="160" t="e">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="H29" s="159">
+        <v>0</v>
+      </c>
+      <c r="I29" s="67"/>
+      <c r="J29" s="159" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="160">
+      <c r="K29" s="159">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="160"/>
-      <c r="M29" s="166">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="L29" s="159"/>
+      <c r="M29" s="165">
+        <f t="shared" si="3"/>
+        <v>325.05947070000002</v>
+      </c>
+      <c r="N29" s="165">
+        <f t="shared" si="8"/>
+        <v>11160.375160700001</v>
+      </c>
+      <c r="O29" s="159">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="166">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="160">
+        <v>5765.6252700000014</v>
+      </c>
+      <c r="P29" s="67">
         <f t="shared" si="5"/>
-        <v>10835.315690000001</v>
-      </c>
-      <c r="P29" s="160">
+        <v>3480.22</v>
+      </c>
+      <c r="Q29" s="159">
+        <f>'Calculo Servicios  (2)'!H27</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="165">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="160">
-        <f>'Calculo Servicios  (2)'!H27</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="166">
-        <f t="shared" si="3"/>
-        <v>10835.315690000001</v>
+        <v>20406.220430700003</v>
       </c>
       <c r="U29" s="95" t="s">
         <v>52</v>
@@ -4259,9 +4248,9 @@
       <c r="M30" s="64"/>
       <c r="N30" s="64"/>
       <c r="O30" s="65"/>
-      <c r="P30" s="65">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="P30" s="65" t="e">
+        <f>#REF!*F30/100</f>
+        <v>#REF!</v>
       </c>
       <c r="Q30" s="65"/>
       <c r="R30" s="109"/>
@@ -4270,15 +4259,15 @@
       </c>
     </row>
     <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="225"/>
-      <c r="B31" s="226"/>
-      <c r="C31" s="226"/>
+      <c r="A31" s="222"/>
+      <c r="B31" s="223"/>
+      <c r="C31" s="223"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
       <c r="F31" s="97"/>
       <c r="G31" s="61">
         <f>SUM(G11:G30)</f>
-        <v>3130164.1365016159</v>
+        <v>2276056.3725747587</v>
       </c>
       <c r="H31" s="61">
         <f>SUM(H11:H30)</f>
@@ -4286,56 +4275,56 @@
       </c>
       <c r="I31" s="62">
         <f>SUM(I11:I30)</f>
-        <v>2672781.3927473403</v>
+        <v>1480247.3410500004</v>
       </c>
       <c r="J31" s="61"/>
       <c r="K31" s="62">
         <f>SUM(K11:K30)</f>
-        <v>457382.74375427479</v>
+        <v>795809.03152475785</v>
       </c>
       <c r="L31" s="61"/>
       <c r="M31" s="60"/>
       <c r="N31" s="59"/>
       <c r="O31" s="62">
         <f>SUM(O11:O30)</f>
-        <v>1463939.0036300013</v>
+        <v>778982.72228999983</v>
       </c>
       <c r="P31" s="62">
-        <f t="shared" ref="P31" si="10">SUM(P11:P30)</f>
-        <v>0</v>
+        <f>SUM(P11:P29)</f>
+        <v>470205.93999999989</v>
       </c>
       <c r="Q31" s="62">
-        <f>SUM(Q11:Q30)</f>
-        <v>340046.28227999998</v>
-      </c>
-      <c r="R31" s="110">
-        <f>O31+N31+P31+Q31</f>
-        <v>1803985.2859100013</v>
+        <f>SUM(Q11:Q29)</f>
+        <v>337250.39328000002</v>
+      </c>
+      <c r="R31" s="62">
+        <f>SUM(R11:R29)</f>
+        <v>2406065.9424022823</v>
       </c>
       <c r="U31" s="94" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="222" t="s">
+      <c r="B32" s="219" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="223"/>
-      <c r="I32" s="223"/>
-      <c r="J32" s="223"/>
-      <c r="K32" s="223"/>
-      <c r="L32" s="223"/>
-      <c r="M32" s="223"/>
-      <c r="N32" s="223"/>
-      <c r="O32" s="223"/>
-      <c r="P32" s="223"/>
-      <c r="Q32" s="223"/>
-      <c r="R32" s="224"/>
+      <c r="C32" s="220"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="220"/>
+      <c r="G32" s="220"/>
+      <c r="H32" s="220"/>
+      <c r="I32" s="220"/>
+      <c r="J32" s="220"/>
+      <c r="K32" s="220"/>
+      <c r="L32" s="220"/>
+      <c r="M32" s="220"/>
+      <c r="N32" s="220"/>
+      <c r="O32" s="220"/>
+      <c r="P32" s="220"/>
+      <c r="Q32" s="220"/>
+      <c r="R32" s="221"/>
       <c r="U32" s="94" t="s">
         <v>55</v>
       </c>
@@ -4355,82 +4344,82 @@
       </c>
     </row>
     <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="216"/>
-      <c r="D34" s="216"/>
-      <c r="E34" s="216"/>
-      <c r="F34" s="216"/>
-      <c r="G34" s="216"/>
-      <c r="H34" s="216"/>
-      <c r="I34" s="216"/>
-      <c r="J34" s="216"/>
-      <c r="K34" s="216"/>
-      <c r="L34" s="216"/>
-      <c r="M34" s="216"/>
-      <c r="N34" s="216"/>
-      <c r="O34" s="216"/>
+      <c r="C34" s="213"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="213"/>
+      <c r="F34" s="213"/>
+      <c r="G34" s="213"/>
+      <c r="H34" s="213"/>
+      <c r="I34" s="213"/>
+      <c r="J34" s="213"/>
+      <c r="K34" s="213"/>
+      <c r="L34" s="213"/>
+      <c r="M34" s="213"/>
+      <c r="N34" s="213"/>
+      <c r="O34" s="213"/>
     </row>
     <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="216"/>
-      <c r="D35" s="216"/>
-      <c r="E35" s="216"/>
-      <c r="F35" s="216"/>
-      <c r="G35" s="216"/>
-      <c r="H35" s="216"/>
-      <c r="I35" s="216"/>
-      <c r="J35" s="216"/>
-      <c r="K35" s="216"/>
-      <c r="L35" s="216"/>
-      <c r="M35" s="216"/>
-      <c r="N35" s="216"/>
-      <c r="O35" s="216"/>
+      <c r="C35" s="213"/>
+      <c r="D35" s="213"/>
+      <c r="E35" s="213"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="213"/>
+      <c r="H35" s="213"/>
+      <c r="I35" s="213"/>
+      <c r="J35" s="213"/>
+      <c r="K35" s="213"/>
+      <c r="L35" s="213"/>
+      <c r="M35" s="213"/>
+      <c r="N35" s="213"/>
+      <c r="O35" s="213"/>
     </row>
     <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="216"/>
-      <c r="D36" s="216"/>
-      <c r="E36" s="216"/>
-      <c r="F36" s="216"/>
-      <c r="G36" s="216"/>
-      <c r="H36" s="216"/>
-      <c r="I36" s="216"/>
-      <c r="J36" s="216"/>
-      <c r="K36" s="216"/>
-      <c r="L36" s="216"/>
-      <c r="M36" s="216"/>
-      <c r="N36" s="216"/>
-      <c r="O36" s="216"/>
+      <c r="C36" s="213"/>
+      <c r="D36" s="213"/>
+      <c r="E36" s="213"/>
+      <c r="F36" s="213"/>
+      <c r="G36" s="213"/>
+      <c r="H36" s="213"/>
+      <c r="I36" s="213"/>
+      <c r="J36" s="213"/>
+      <c r="K36" s="213"/>
+      <c r="L36" s="213"/>
+      <c r="M36" s="213"/>
+      <c r="N36" s="213"/>
+      <c r="O36" s="213"/>
     </row>
     <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="216"/>
-      <c r="D37" s="216"/>
-      <c r="E37" s="216"/>
-      <c r="F37" s="216"/>
-      <c r="G37" s="216"/>
-      <c r="H37" s="216"/>
-      <c r="I37" s="216"/>
-      <c r="J37" s="216"/>
-      <c r="K37" s="216"/>
-      <c r="L37" s="216"/>
-      <c r="M37" s="216"/>
-      <c r="N37" s="216"/>
-      <c r="O37" s="216"/>
+      <c r="C37" s="213"/>
+      <c r="D37" s="213"/>
+      <c r="E37" s="213"/>
+      <c r="F37" s="213"/>
+      <c r="G37" s="213"/>
+      <c r="H37" s="213"/>
+      <c r="I37" s="213"/>
+      <c r="J37" s="213"/>
+      <c r="K37" s="213"/>
+      <c r="L37" s="213"/>
+      <c r="M37" s="213"/>
+      <c r="N37" s="213"/>
+      <c r="O37" s="213"/>
     </row>
     <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="216"/>
-      <c r="D38" s="216"/>
-      <c r="E38" s="216"/>
-      <c r="F38" s="216"/>
-      <c r="G38" s="216"/>
-      <c r="H38" s="216"/>
-      <c r="I38" s="216"/>
-      <c r="J38" s="216"/>
-      <c r="K38" s="216"/>
-      <c r="L38" s="216"/>
-      <c r="M38" s="216"/>
-      <c r="N38" s="216"/>
-      <c r="O38" s="216"/>
+      <c r="C38" s="213"/>
+      <c r="D38" s="213"/>
+      <c r="E38" s="213"/>
+      <c r="F38" s="213"/>
+      <c r="G38" s="213"/>
+      <c r="H38" s="213"/>
+      <c r="I38" s="213"/>
+      <c r="J38" s="213"/>
+      <c r="K38" s="213"/>
+      <c r="L38" s="213"/>
+      <c r="M38" s="213"/>
+      <c r="N38" s="213"/>
+      <c r="O38" s="213"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C34:O38"/>
     <mergeCell ref="M4:R4"/>
     <mergeCell ref="A1:R1"/>
@@ -4438,6 +4427,7 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToWidth="0" orientation="landscape" r:id="rId1"/>
@@ -4450,95 +4440,95 @@
   <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="115" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="115" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="115" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="115" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="115" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="115" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="115" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="115"/>
-    <col min="13" max="13" width="14.7109375" style="115" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="115" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="115"/>
+    <col min="1" max="1" width="12.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="114" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="114" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="114" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="114"/>
+    <col min="13" max="13" width="14.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="114" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="114"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="225" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="230"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="227"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="156"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="155" t="s">
+      <c r="A2" s="155"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="152"/>
+      <c r="E2" s="151"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="154">
+      <c r="A3" s="153">
         <f>13+28+19</f>
         <v>60</v>
       </c>
       <c r="B3" s="108">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="153">
+      <c r="C3" s="152">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="153">
+      <c r="D3" s="152">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="152" t="s">
+      <c r="E3" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" s="114" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="151"/>
-      <c r="B4" s="150"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="149"/>
+      <c r="A4" s="150"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="148"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
+      <c r="A5" s="147"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
     </row>
     <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
+      <c r="A6" s="147"/>
+      <c r="B6" s="147"/>
+      <c r="C6" s="147"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="147"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="232"/>
-      <c r="C7" s="232"/>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="233"/>
-      <c r="L7" s="115" t="s">
+      <c r="B7" s="229"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="230"/>
+      <c r="L7" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="115" t="s">
+      <c r="M7" s="114" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4546,50 +4536,50 @@
       <c r="A8" s="107">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="146" t="s">
+      <c r="B8" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="146" t="s">
+      <c r="D8" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="147">
+      <c r="E8" s="146">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="146" t="s">
+      <c r="F8" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="146" t="s">
+      <c r="G8" s="145" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="145" t="s">
+      <c r="H8" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="141">
+      <c r="K8" s="140">
         <v>19</v>
       </c>
-      <c r="L8" s="127">
+      <c r="L8" s="126">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="127">
+      <c r="M8" s="126">
         <v>2365.2600000000002</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="144" t="s">
+      <c r="A9" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="141">
+      <c r="B9" s="140">
         <v>1617</v>
       </c>
-      <c r="C9" s="141">
+      <c r="C9" s="140">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="141">
+      <c r="D9" s="140">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
@@ -4609,18 +4599,18 @@
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="115">
+      <c r="K9" s="114">
         <v>106</v>
       </c>
-      <c r="L9" s="127">
+      <c r="L9" s="126">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="115">
+      <c r="M9" s="114">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="115" t="s">
+      <c r="N9" s="114" t="s">
         <v>69</v>
       </c>
       <c r="O9" s="106">
@@ -4628,17 +4618,17 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="142" t="s">
+      <c r="A10" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="141">
+      <c r="B10" s="140">
         <v>4104</v>
       </c>
-      <c r="C10" s="141">
+      <c r="C10" s="140">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="141">
+      <c r="D10" s="140">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
@@ -4658,18 +4648,18 @@
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="114">
         <v>60</v>
       </c>
-      <c r="L10" s="127">
+      <c r="L10" s="126">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="114">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="115" t="s">
+      <c r="N10" s="114" t="s">
         <v>68</v>
       </c>
       <c r="O10" s="105">
@@ -4677,17 +4667,17 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="142" t="s">
+      <c r="A11" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="141">
+      <c r="B11" s="140">
         <v>7644</v>
       </c>
-      <c r="C11" s="141">
+      <c r="C11" s="140">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="141">
+      <c r="D11" s="140">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
@@ -4707,35 +4697,35 @@
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="115">
+      <c r="K11" s="114">
         <v>79</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="126">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="115">
+      <c r="M11" s="114">
         <v>0.03</v>
       </c>
-      <c r="N11" s="115" t="s">
+      <c r="N11" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="126">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="142" t="s">
+      <c r="A12" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="141">
+      <c r="B12" s="140">
         <v>6554</v>
       </c>
-      <c r="C12" s="141">
+      <c r="C12" s="140">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="141">
+      <c r="D12" s="140">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
@@ -4755,34 +4745,34 @@
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="115">
+      <c r="K12" s="114">
         <v>89</v>
       </c>
-      <c r="L12" s="127">
+      <c r="L12" s="126">
         <v>400</v>
       </c>
-      <c r="M12" s="115">
+      <c r="M12" s="114">
         <v>253</v>
       </c>
-      <c r="N12" s="115" t="s">
+      <c r="N12" s="114" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="115">
+      <c r="O12" s="114">
         <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="142" t="s">
+      <c r="A13" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="141">
+      <c r="B13" s="140">
         <v>7564</v>
       </c>
-      <c r="C13" s="141">
+      <c r="C13" s="140">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="141">
+      <c r="D13" s="140">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
@@ -4802,30 +4792,30 @@
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="115">
+      <c r="K13" s="114">
         <v>140</v>
       </c>
-      <c r="L13" s="143">
+      <c r="L13" s="142">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="115">
+      <c r="M13" s="114">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="142" t="s">
+      <c r="A14" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="141">
+      <c r="B14" s="140">
         <v>10119</v>
       </c>
-      <c r="C14" s="141">
+      <c r="C14" s="140">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="141">
+      <c r="D14" s="140">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
@@ -4845,22 +4835,22 @@
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="115">
+      <c r="K14" s="114">
         <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="141">
+      <c r="B15" s="140">
         <v>8986</v>
       </c>
-      <c r="C15" s="141">
+      <c r="C15" s="140">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="141">
+      <c r="D15" s="140">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
@@ -4880,26 +4870,26 @@
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="115">
+      <c r="K15" s="114">
         <v>221</v>
       </c>
-      <c r="L15" s="115">
+      <c r="L15" s="114">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="141">
+      <c r="B16" s="140">
         <v>7032</v>
       </c>
-      <c r="C16" s="141">
+      <c r="C16" s="140">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="141">
+      <c r="D16" s="140">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -4919,22 +4909,22 @@
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="115">
+      <c r="K16" s="114">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="142" t="s">
+      <c r="A17" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="141">
+      <c r="B17" s="140">
         <v>1623</v>
       </c>
-      <c r="C17" s="141">
+      <c r="C17" s="140">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="141">
+      <c r="D17" s="140">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -4954,22 +4944,22 @@
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="115">
+      <c r="K17" s="114">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="142" t="s">
+      <c r="A18" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="141">
+      <c r="B18" s="140">
         <v>3932</v>
       </c>
-      <c r="C18" s="141">
+      <c r="C18" s="140">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="141">
+      <c r="D18" s="140">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
@@ -4989,22 +4979,22 @@
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="115">
+      <c r="K18" s="114">
         <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="142" t="s">
+      <c r="A19" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="141">
+      <c r="B19" s="140">
         <v>6887</v>
       </c>
-      <c r="C19" s="141">
+      <c r="C19" s="140">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="141">
+      <c r="D19" s="140">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -5024,22 +5014,22 @@
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="115">
+      <c r="K19" s="114">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="142" t="s">
+      <c r="A20" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="141">
+      <c r="B20" s="140">
         <v>1884</v>
       </c>
-      <c r="C20" s="141">
+      <c r="C20" s="140">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="141">
+      <c r="D20" s="140">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
@@ -5061,23 +5051,23 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="140" t="s">
+      <c r="A21" s="139" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="139"/>
-      <c r="C21" s="139"/>
-      <c r="D21" s="138">
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="137">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="137"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
       <c r="H21" s="101">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="127">
+      <c r="J21" s="126">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
@@ -5087,70 +5077,70 @@
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="135"/>
+      <c r="L22" s="134"/>
     </row>
     <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="99">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="134" t="s">
+      <c r="B23" s="133" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="133"/>
-      <c r="J25" s="115">
+      <c r="A25" s="132"/>
+      <c r="J25" s="114">
         <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="J26" s="115">
+      <c r="J26" s="114">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="115">
+      <c r="J27" s="114">
         <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="234" t="s">
+      <c r="B28" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="235"/>
-      <c r="D28" s="235"/>
-      <c r="E28" s="235"/>
-      <c r="F28" s="236"/>
-      <c r="J28" s="115">
+      <c r="C28" s="232"/>
+      <c r="D28" s="232"/>
+      <c r="E28" s="232"/>
+      <c r="F28" s="233"/>
+      <c r="J28" s="114">
         <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B29" s="132" t="s">
+      <c r="B29" s="131" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="131" t="s">
+      <c r="C29" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="131" t="s">
+      <c r="D29" s="130" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="131" t="s">
+      <c r="E29" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="130" t="s">
+      <c r="F29" s="129" t="s">
         <v>133</v>
       </c>
-      <c r="J29" s="115">
+      <c r="J29" s="114">
         <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="126" t="s">
+      <c r="B30" s="125" t="s">
         <v>132</v>
       </c>
       <c r="C30" s="103">
@@ -5159,21 +5149,21 @@
       <c r="D30" s="103">
         <v>0</v>
       </c>
-      <c r="E30" s="124"/>
+      <c r="E30" s="123"/>
       <c r="F30" s="102">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="129">
+      <c r="J30" s="128">
         <v>215</v>
       </c>
-      <c r="M30" s="115">
+      <c r="M30" s="114">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="125" t="s">
         <v>131</v>
       </c>
       <c r="C31" s="103">
@@ -5182,17 +5172,17 @@
       <c r="D31" s="103">
         <v>0</v>
       </c>
-      <c r="E31" s="124"/>
+      <c r="E31" s="123"/>
       <c r="F31" s="102">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="115">
+      <c r="J31" s="114">
         <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="126" t="s">
+      <c r="B32" s="125" t="s">
         <v>130</v>
       </c>
       <c r="C32" s="103">
@@ -5201,17 +5191,17 @@
       <c r="D32" s="103">
         <v>0</v>
       </c>
-      <c r="E32" s="124"/>
+      <c r="E32" s="123"/>
       <c r="F32" s="102">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="115">
+      <c r="J32" s="114">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="126" t="s">
+      <c r="B33" s="125" t="s">
         <v>129</v>
       </c>
       <c r="C33" s="103">
@@ -5220,21 +5210,21 @@
       <c r="D33" s="103">
         <v>0</v>
       </c>
-      <c r="E33" s="124"/>
+      <c r="E33" s="123"/>
       <c r="F33" s="102">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="115">
+      <c r="J33" s="114">
         <v>45</v>
       </c>
-      <c r="K33" s="128">
+      <c r="K33" s="127">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="126" t="s">
+      <c r="B34" s="125" t="s">
         <v>128</v>
       </c>
       <c r="C34" s="103">
@@ -5243,17 +5233,17 @@
       <c r="D34" s="103">
         <v>0</v>
       </c>
-      <c r="E34" s="124"/>
+      <c r="E34" s="123"/>
       <c r="F34" s="102">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="115">
+      <c r="J34" s="114">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="125" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="103">
@@ -5262,17 +5252,17 @@
       <c r="D35" s="103">
         <v>0</v>
       </c>
-      <c r="E35" s="124"/>
+      <c r="E35" s="123"/>
       <c r="F35" s="102">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="115">
+      <c r="J35" s="114">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="126" t="s">
+      <c r="B36" s="125" t="s">
         <v>126</v>
       </c>
       <c r="C36" s="103">
@@ -5281,176 +5271,176 @@
       <c r="D36" s="103">
         <v>0</v>
       </c>
-      <c r="E36" s="124"/>
+      <c r="E36" s="123"/>
       <c r="F36" s="102">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="115">
+      <c r="J36" s="114">
         <v>136</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="126" t="s">
+      <c r="B37" s="125" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="125">
+      <c r="C37" s="124">
         <v>4000</v>
       </c>
       <c r="D37" s="103">
         <v>0</v>
       </c>
-      <c r="E37" s="124"/>
+      <c r="E37" s="123"/>
       <c r="F37" s="102">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="126" t="s">
+      <c r="B38" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="125">
+      <c r="C38" s="124">
         <v>4000</v>
       </c>
-      <c r="D38" s="125">
+      <c r="D38" s="124">
         <v>3500</v>
       </c>
-      <c r="E38" s="124" t="s">
+      <c r="E38" s="123" t="s">
         <v>123</v>
       </c>
       <c r="F38" s="102">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="127">
+      <c r="M38" s="126">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="126" t="s">
+      <c r="B39" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="125">
+      <c r="C39" s="124">
         <v>4000</v>
       </c>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
+      <c r="D39" s="123"/>
+      <c r="E39" s="123"/>
       <c r="F39" s="102">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="126" t="s">
+      <c r="B40" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="125">
+      <c r="C40" s="124">
         <v>4000</v>
       </c>
-      <c r="D40" s="124"/>
-      <c r="E40" s="124"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
       <c r="F40" s="102">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="126" t="s">
+      <c r="B41" s="125" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="125">
+      <c r="C41" s="124">
         <v>4000</v>
       </c>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
       <c r="F41" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="126" t="s">
+      <c r="B42" s="125" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="125">
-        <v>0</v>
-      </c>
-      <c r="D42" s="124"/>
-      <c r="E42" s="124"/>
+      <c r="C42" s="124">
+        <v>0</v>
+      </c>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
       <c r="F42" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="126" t="s">
+      <c r="B43" s="125" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="125">
-        <v>0</v>
-      </c>
-      <c r="D43" s="124"/>
-      <c r="E43" s="124"/>
+      <c r="C43" s="124">
+        <v>0</v>
+      </c>
+      <c r="D43" s="123"/>
+      <c r="E43" s="123"/>
       <c r="F43" s="102">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="123" t="s">
+      <c r="B44" s="122" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="122">
-        <v>0</v>
-      </c>
-      <c r="D44" s="121"/>
-      <c r="E44" s="121"/>
-      <c r="F44" s="120">
+      <c r="C44" s="121">
+        <v>0</v>
+      </c>
+      <c r="D44" s="120"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="119">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="123" t="s">
+      <c r="B45" s="122" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="122">
-        <v>0</v>
-      </c>
-      <c r="D45" s="121"/>
-      <c r="E45" s="121"/>
-      <c r="F45" s="120">
+      <c r="C45" s="121">
+        <v>0</v>
+      </c>
+      <c r="D45" s="120"/>
+      <c r="E45" s="120"/>
+      <c r="F45" s="119">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="123" t="s">
+      <c r="B46" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="122">
-        <v>0</v>
-      </c>
-      <c r="D46" s="121"/>
-      <c r="E46" s="121"/>
-      <c r="F46" s="120">
+      <c r="C46" s="121">
+        <v>0</v>
+      </c>
+      <c r="D46" s="120"/>
+      <c r="E46" s="120"/>
+      <c r="F46" s="119">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
     <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="119" t="s">
+      <c r="B47" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="118">
+      <c r="C47" s="117">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="116">
+      <c r="D47" s="116"/>
+      <c r="E47" s="116"/>
+      <c r="F47" s="115">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>
